--- a/Deliverables/BOM/eSpark-BOM-v2.0 Boards_PCBWay.xlsx
+++ b/Deliverables/BOM/eSpark-BOM-v2.0 Boards_PCBWay.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="25225"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="25408"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\Melih-SoundSensor\Deliverables\BOM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\Melih-SoundSensor\Deliverables\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{211C0C1F-8B88-4ACF-9851-6FD70D8EC895}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE9EB3AE-8AFA-4F59-A2FA-2EE31933FE47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14016" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="240">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="239">
   <si>
     <t>S. No.</t>
   </si>
@@ -44,9 +44,6 @@
   </si>
   <si>
     <t>Value</t>
-  </si>
-  <si>
-    <t>Quantity (Per Board)</t>
   </si>
   <si>
     <t>Capacitor</t>
@@ -754,7 +751,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.0000"/>
   </numFmts>
-  <fonts count="16">
+  <fonts count="15">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -815,14 +812,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="8"/>
       <name val="Calibri"/>
       <charset val="134"/>
@@ -874,7 +863,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -901,24 +890,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC000"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="27">
+  <borders count="21">
     <border>
       <left/>
       <right/>
@@ -1176,90 +1153,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color auto="1"/>
       </left>
@@ -1281,12 +1174,12 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="112">
+  <cellXfs count="83">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1301,204 +1194,221 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="11" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="5" borderId="11" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="17" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="11" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="6" borderId="11" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="17" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1506,112 +1416,10 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="26" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1890,37 +1698,35 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K66"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <dimension ref="A1:I66"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="6.140625" style="2" customWidth="1"/>
-    <col min="2" max="2" width="14.42578125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="47.5703125" style="10" customWidth="1"/>
-    <col min="4" max="4" width="35.140625" style="11" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.5703125" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="28.42578125" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.28515625" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.109375" style="2" customWidth="1"/>
+    <col min="2" max="2" width="14.44140625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="47.5546875" style="9" customWidth="1"/>
+    <col min="4" max="4" width="35.109375" style="10" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.5546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="28.44140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.33203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.44140625" style="2" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="21.85546875" style="1" customWidth="1"/>
-    <col min="11" max="16384" width="9" style="1"/>
+    <col min="10" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="16.5" thickBot="1">
-      <c r="A1" s="74" t="s">
-        <v>117</v>
-      </c>
-      <c r="B1" s="75"/>
-      <c r="C1" s="75"/>
-      <c r="D1" s="75"/>
-      <c r="E1" s="75"/>
-      <c r="F1" s="75"/>
-      <c r="G1" s="75"/>
-      <c r="H1" s="75"/>
-      <c r="I1" s="75"/>
-      <c r="J1" s="88"/>
-    </row>
-    <row r="2" spans="1:11" ht="16.5" thickBot="1">
+    <row r="1" spans="1:9" ht="16.2" thickBot="1">
+      <c r="A1" s="79" t="s">
+        <v>116</v>
+      </c>
+      <c r="B1" s="80"/>
+      <c r="C1" s="80"/>
+      <c r="D1" s="80"/>
+      <c r="E1" s="80"/>
+      <c r="F1" s="80"/>
+      <c r="G1" s="80"/>
+      <c r="H1" s="80"/>
+      <c r="I1" s="80"/>
+    </row>
+    <row r="2" spans="1:9" ht="16.2" thickBot="1">
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
@@ -1945,1590 +1751,1381 @@
       <c r="H2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="I2" s="55" t="s">
-        <v>200</v>
-      </c>
-      <c r="J2" s="5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" ht="15.75" thickBot="1">
+      <c r="I2" s="49" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="15" thickBot="1">
       <c r="A3" s="6">
         <v>1</v>
       </c>
-      <c r="B3" s="76" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="30" t="s">
+      <c r="B3" s="75" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="28" t="s">
+        <v>33</v>
+      </c>
+      <c r="D3" s="47" t="s">
+        <v>123</v>
+      </c>
+      <c r="E3" s="29" t="s">
         <v>34</v>
       </c>
-      <c r="D3" s="53" t="s">
-        <v>124</v>
-      </c>
-      <c r="E3" s="32" t="s">
+      <c r="F3" s="29" t="s">
         <v>35</v>
       </c>
-      <c r="F3" s="32" t="s">
-        <v>36</v>
-      </c>
-      <c r="G3" s="14" t="s">
-        <v>95</v>
-      </c>
-      <c r="H3" s="31" t="s">
-        <v>14</v>
-      </c>
-      <c r="I3" s="15">
+      <c r="G3" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="H3" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="I3" s="13">
         <v>100</v>
       </c>
-      <c r="J3" s="89">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" ht="15.75" thickBot="1">
+    </row>
+    <row r="4" spans="1:9" ht="15" thickBot="1">
       <c r="A4" s="6">
         <v>2</v>
       </c>
-      <c r="B4" s="77"/>
-      <c r="C4" s="33" t="s">
-        <v>15</v>
-      </c>
-      <c r="D4" s="42" t="s">
+      <c r="B4" s="76"/>
+      <c r="C4" s="30" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" s="36" t="s">
+        <v>36</v>
+      </c>
+      <c r="E4" s="31" t="s">
+        <v>34</v>
+      </c>
+      <c r="F4" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="E4" s="35" t="s">
-        <v>35</v>
-      </c>
-      <c r="F4" s="35" t="s">
-        <v>38</v>
-      </c>
-      <c r="G4" s="17" t="s">
-        <v>96</v>
-      </c>
-      <c r="H4" s="34" t="s">
-        <v>54</v>
-      </c>
-      <c r="I4" s="19">
+      <c r="G4" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="H4" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="I4" s="17">
         <v>40</v>
       </c>
-      <c r="J4" s="90">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" ht="39" thickBot="1">
+    </row>
+    <row r="5" spans="1:9" ht="42" thickBot="1">
       <c r="A5" s="6">
         <v>3</v>
       </c>
-      <c r="B5" s="77"/>
-      <c r="C5" s="33" t="s">
+      <c r="B5" s="76"/>
+      <c r="C5" s="30" t="s">
+        <v>38</v>
+      </c>
+      <c r="D5" s="46" t="s">
+        <v>119</v>
+      </c>
+      <c r="E5" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="F5" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="D5" s="52" t="s">
-        <v>120</v>
-      </c>
-      <c r="E5" s="34" t="s">
-        <v>35</v>
-      </c>
-      <c r="F5" s="34" t="s">
-        <v>40</v>
-      </c>
-      <c r="G5" s="17" t="s">
-        <v>97</v>
-      </c>
-      <c r="H5" s="34" t="s">
-        <v>10</v>
-      </c>
-      <c r="I5" s="19">
+      <c r="G5" s="15" t="s">
+        <v>96</v>
+      </c>
+      <c r="H5" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="I5" s="17">
         <v>400</v>
       </c>
-      <c r="J5" s="90">
-        <v>19</v>
-      </c>
-      <c r="K5" s="9"/>
-    </row>
-    <row r="6" spans="1:11" ht="15.75" thickBot="1">
+    </row>
+    <row r="6" spans="1:9" ht="15" thickBot="1">
       <c r="A6" s="6">
         <v>4</v>
       </c>
-      <c r="B6" s="77"/>
-      <c r="C6" s="33" t="s">
+      <c r="B6" s="76"/>
+      <c r="C6" s="30" t="s">
+        <v>40</v>
+      </c>
+      <c r="D6" s="36" t="s">
         <v>41</v>
       </c>
-      <c r="D6" s="42" t="s">
+      <c r="E6" s="31" t="s">
         <v>42</v>
       </c>
-      <c r="E6" s="35" t="s">
+      <c r="F6" s="31" t="s">
         <v>43</v>
       </c>
-      <c r="F6" s="35" t="s">
-        <v>44</v>
-      </c>
-      <c r="G6" s="17" t="s">
-        <v>98</v>
-      </c>
-      <c r="H6" s="34" t="s">
-        <v>55</v>
-      </c>
-      <c r="I6" s="19">
+      <c r="G6" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="H6" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="I6" s="17">
         <v>200</v>
       </c>
-      <c r="J6" s="90">
-        <v>8</v>
-      </c>
-      <c r="K6" s="9"/>
-    </row>
-    <row r="7" spans="1:11" ht="15.75" thickBot="1">
+    </row>
+    <row r="7" spans="1:9" ht="15" thickBot="1">
       <c r="A7" s="6">
         <v>5</v>
       </c>
-      <c r="B7" s="77"/>
-      <c r="C7" s="33" t="s">
+      <c r="B7" s="76"/>
+      <c r="C7" s="30" t="s">
+        <v>120</v>
+      </c>
+      <c r="D7" s="36" t="s">
         <v>121</v>
       </c>
-      <c r="D7" s="42" t="s">
+      <c r="E7" s="31" t="s">
         <v>122</v>
       </c>
-      <c r="E7" s="35" t="s">
-        <v>123</v>
-      </c>
-      <c r="F7" s="18" t="s">
-        <v>163</v>
-      </c>
-      <c r="G7" s="17" t="s">
+      <c r="F7" s="16" t="s">
+        <v>162</v>
+      </c>
+      <c r="G7" s="15" t="s">
+        <v>154</v>
+      </c>
+      <c r="H7" s="17" t="s">
         <v>155</v>
       </c>
-      <c r="H7" s="34" t="s">
-        <v>156</v>
-      </c>
-      <c r="I7" s="19">
+      <c r="I7" s="17">
         <v>100</v>
       </c>
-      <c r="J7" s="90">
-        <v>1</v>
-      </c>
-      <c r="K7" s="9"/>
-    </row>
-    <row r="8" spans="1:11" ht="51.75" thickBot="1">
+    </row>
+    <row r="8" spans="1:9" ht="55.8" thickBot="1">
       <c r="A8" s="6">
         <v>6</v>
       </c>
-      <c r="B8" s="77"/>
-      <c r="C8" s="33" t="s">
+      <c r="B8" s="76"/>
+      <c r="C8" s="30" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" s="46" t="s">
+        <v>171</v>
+      </c>
+      <c r="E8" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="F8" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="D8" s="52" t="s">
-        <v>172</v>
-      </c>
-      <c r="E8" s="34" t="s">
-        <v>35</v>
-      </c>
-      <c r="F8" s="34" t="s">
+      <c r="G8" s="15" t="s">
+        <v>98</v>
+      </c>
+      <c r="H8" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G8" s="17" t="s">
-        <v>99</v>
-      </c>
-      <c r="H8" s="34" t="s">
-        <v>13</v>
-      </c>
-      <c r="I8" s="19">
+      <c r="I8" s="17">
         <v>600</v>
       </c>
-      <c r="J8" s="90">
-        <v>29</v>
-      </c>
-      <c r="K8" s="9"/>
-    </row>
-    <row r="9" spans="1:11" ht="15.75" thickBot="1">
+    </row>
+    <row r="9" spans="1:9" ht="15" thickBot="1">
       <c r="A9" s="6">
         <v>7</v>
       </c>
-      <c r="B9" s="77"/>
-      <c r="C9" s="33" t="s">
+      <c r="B9" s="76"/>
+      <c r="C9" s="30" t="s">
+        <v>44</v>
+      </c>
+      <c r="D9" s="36" t="s">
         <v>45</v>
       </c>
-      <c r="D9" s="42" t="s">
+      <c r="E9" s="31" t="s">
+        <v>34</v>
+      </c>
+      <c r="F9" s="31" t="s">
         <v>46</v>
       </c>
-      <c r="E9" s="35" t="s">
-        <v>35</v>
-      </c>
-      <c r="F9" s="35" t="s">
-        <v>47</v>
-      </c>
-      <c r="G9" s="21" t="s">
-        <v>100</v>
-      </c>
-      <c r="H9" s="34" t="s">
-        <v>56</v>
-      </c>
-      <c r="I9" s="20">
+      <c r="G9" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="H9" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="I9" s="18">
         <v>30</v>
       </c>
-      <c r="J9" s="90">
-        <v>1</v>
-      </c>
-      <c r="K9" s="9"/>
-    </row>
-    <row r="10" spans="1:11" ht="15.75" thickBot="1">
+    </row>
+    <row r="10" spans="1:9" ht="15" thickBot="1">
       <c r="A10" s="6">
         <v>8</v>
       </c>
-      <c r="B10" s="77"/>
-      <c r="C10" s="33" t="s">
+      <c r="B10" s="76"/>
+      <c r="C10" s="30" t="s">
+        <v>47</v>
+      </c>
+      <c r="D10" s="36" t="s">
         <v>48</v>
       </c>
-      <c r="D10" s="42" t="s">
+      <c r="E10" s="31" t="s">
+        <v>34</v>
+      </c>
+      <c r="F10" s="31" t="s">
         <v>49</v>
       </c>
-      <c r="E10" s="35" t="s">
-        <v>35</v>
-      </c>
-      <c r="F10" s="35" t="s">
-        <v>50</v>
-      </c>
-      <c r="G10" s="17" t="s">
-        <v>101</v>
-      </c>
-      <c r="H10" s="34" t="s">
-        <v>57</v>
-      </c>
-      <c r="I10" s="20">
+      <c r="G10" s="15" t="s">
+        <v>100</v>
+      </c>
+      <c r="H10" s="17" t="s">
+        <v>56</v>
+      </c>
+      <c r="I10" s="18">
         <v>200</v>
       </c>
-      <c r="J10" s="90">
-        <v>6</v>
-      </c>
-      <c r="K10" s="9"/>
-    </row>
-    <row r="11" spans="1:11" ht="26.25" thickBot="1">
+    </row>
+    <row r="11" spans="1:9" ht="28.2" thickBot="1">
       <c r="A11" s="6">
         <v>9</v>
       </c>
-      <c r="B11" s="77"/>
-      <c r="C11" s="33" t="s">
+      <c r="B11" s="76"/>
+      <c r="C11" s="30" t="s">
+        <v>50</v>
+      </c>
+      <c r="D11" s="46" t="s">
         <v>51</v>
       </c>
-      <c r="D11" s="52" t="s">
+      <c r="E11" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="F11" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="E11" s="34" t="s">
-        <v>35</v>
-      </c>
-      <c r="F11" s="34" t="s">
-        <v>53</v>
-      </c>
-      <c r="G11" s="17" t="s">
-        <v>102</v>
-      </c>
-      <c r="H11" s="34" t="s">
-        <v>58</v>
-      </c>
-      <c r="I11" s="20">
+      <c r="G11" s="15" t="s">
+        <v>101</v>
+      </c>
+      <c r="H11" s="17" t="s">
+        <v>57</v>
+      </c>
+      <c r="I11" s="18">
         <v>350</v>
       </c>
-      <c r="J11" s="90">
-        <v>16</v>
-      </c>
-      <c r="K11" s="9"/>
-    </row>
-    <row r="12" spans="1:11" ht="15.75" thickBot="1">
+    </row>
+    <row r="12" spans="1:9" ht="15" thickBot="1">
       <c r="A12" s="6">
         <v>10</v>
       </c>
-      <c r="B12" s="77"/>
-      <c r="C12" s="33" t="s">
+      <c r="B12" s="76"/>
+      <c r="C12" s="30" t="s">
+        <v>124</v>
+      </c>
+      <c r="D12" s="36" t="s">
         <v>125</v>
       </c>
-      <c r="D12" s="42" t="s">
+      <c r="E12" s="31" t="s">
+        <v>34</v>
+      </c>
+      <c r="F12" s="31" t="s">
         <v>126</v>
       </c>
-      <c r="E12" s="35" t="s">
-        <v>35</v>
-      </c>
-      <c r="F12" s="35" t="s">
-        <v>127</v>
-      </c>
-      <c r="G12" s="17" t="s">
+      <c r="G12" s="15" t="s">
+        <v>156</v>
+      </c>
+      <c r="H12" s="17" t="s">
         <v>157</v>
       </c>
-      <c r="H12" s="34" t="s">
-        <v>158</v>
-      </c>
-      <c r="I12" s="20">
+      <c r="I12" s="18">
         <v>50</v>
       </c>
-      <c r="J12" s="90">
-        <v>1</v>
-      </c>
-      <c r="K12" s="9"/>
-    </row>
-    <row r="13" spans="1:11" ht="15.75" thickBot="1">
+    </row>
+    <row r="13" spans="1:9" ht="15" thickBot="1">
       <c r="A13" s="6">
         <v>11</v>
       </c>
-      <c r="B13" s="77"/>
-      <c r="C13" s="33" t="s">
+      <c r="B13" s="76"/>
+      <c r="C13" s="30" t="s">
+        <v>127</v>
+      </c>
+      <c r="D13" s="46" t="s">
         <v>128</v>
       </c>
-      <c r="D13" s="52" t="s">
-        <v>129</v>
-      </c>
-      <c r="E13" s="34" t="s">
-        <v>123</v>
-      </c>
-      <c r="F13" s="18" t="s">
-        <v>164</v>
-      </c>
-      <c r="G13" s="17" t="s">
+      <c r="E13" s="17" t="s">
+        <v>122</v>
+      </c>
+      <c r="F13" s="16" t="s">
+        <v>163</v>
+      </c>
+      <c r="G13" s="15" t="s">
+        <v>158</v>
+      </c>
+      <c r="H13" s="17" t="s">
         <v>159</v>
       </c>
-      <c r="H13" s="34" t="s">
-        <v>160</v>
-      </c>
-      <c r="I13" s="20">
+      <c r="I13" s="18">
         <v>100</v>
       </c>
-      <c r="J13" s="90">
-        <v>1</v>
-      </c>
-      <c r="K13" s="9"/>
-    </row>
-    <row r="14" spans="1:11" ht="15.75" thickBot="1">
+    </row>
+    <row r="14" spans="1:9" ht="15" thickBot="1">
       <c r="A14" s="6">
         <v>12</v>
       </c>
-      <c r="B14" s="77"/>
-      <c r="C14" s="33" t="s">
+      <c r="B14" s="76"/>
+      <c r="C14" s="30" t="s">
+        <v>172</v>
+      </c>
+      <c r="D14" s="36" t="s">
         <v>173</v>
       </c>
-      <c r="D14" s="42" t="s">
+      <c r="E14" s="31" t="s">
+        <v>17</v>
+      </c>
+      <c r="F14" s="31" t="s">
         <v>174</v>
       </c>
-      <c r="E14" s="35" t="s">
-        <v>18</v>
-      </c>
-      <c r="F14" s="35" t="s">
-        <v>175</v>
-      </c>
-      <c r="G14" s="17" t="s">
+      <c r="G14" s="15" t="s">
+        <v>181</v>
+      </c>
+      <c r="H14" s="17" t="s">
         <v>182</v>
       </c>
-      <c r="H14" s="34" t="s">
-        <v>183</v>
-      </c>
-      <c r="I14" s="20">
+      <c r="I14" s="18">
         <v>100</v>
       </c>
-      <c r="J14" s="90">
-        <v>1</v>
-      </c>
-      <c r="K14" s="9"/>
-    </row>
-    <row r="15" spans="1:11" ht="15.75" thickBot="1">
+    </row>
+    <row r="15" spans="1:9" ht="15" thickBot="1">
       <c r="A15" s="6">
         <v>13</v>
       </c>
-      <c r="B15" s="77"/>
-      <c r="C15" s="33" t="s">
+      <c r="B15" s="76"/>
+      <c r="C15" s="30" t="s">
+        <v>175</v>
+      </c>
+      <c r="D15" s="36" t="s">
         <v>176</v>
       </c>
-      <c r="D15" s="42" t="s">
+      <c r="E15" s="31" t="s">
+        <v>17</v>
+      </c>
+      <c r="F15" s="31" t="s">
         <v>177</v>
       </c>
-      <c r="E15" s="35" t="s">
-        <v>18</v>
-      </c>
-      <c r="F15" s="35" t="s">
-        <v>178</v>
-      </c>
-      <c r="G15" s="17" t="s">
+      <c r="G15" s="15" t="s">
+        <v>183</v>
+      </c>
+      <c r="H15" s="17" t="s">
         <v>184</v>
       </c>
-      <c r="H15" s="34" t="s">
-        <v>185</v>
-      </c>
-      <c r="I15" s="20">
+      <c r="I15" s="18">
         <v>50</v>
       </c>
-      <c r="J15" s="90">
-        <v>2</v>
-      </c>
-      <c r="K15" s="9"/>
-    </row>
-    <row r="16" spans="1:11" ht="15.75" thickBot="1">
+    </row>
+    <row r="16" spans="1:9" ht="15" thickBot="1">
       <c r="A16" s="6">
         <v>14</v>
       </c>
-      <c r="B16" s="77"/>
-      <c r="C16" s="33" t="s">
+      <c r="B16" s="76"/>
+      <c r="C16" s="30" t="s">
+        <v>202</v>
+      </c>
+      <c r="D16" s="36" t="s">
         <v>203</v>
       </c>
-      <c r="D16" s="42" t="s">
+      <c r="E16" s="31" t="s">
+        <v>34</v>
+      </c>
+      <c r="F16" s="31" t="s">
         <v>204</v>
       </c>
-      <c r="E16" s="35" t="s">
-        <v>35</v>
-      </c>
-      <c r="F16" s="35" t="s">
-        <v>205</v>
-      </c>
-      <c r="G16" s="17" t="s">
+      <c r="G16" s="15" t="s">
+        <v>208</v>
+      </c>
+      <c r="H16" s="17" t="s">
         <v>209</v>
       </c>
-      <c r="H16" s="34" t="s">
-        <v>210</v>
-      </c>
-      <c r="I16" s="20">
+      <c r="I16" s="18">
         <v>50</v>
       </c>
-      <c r="J16" s="90">
-        <v>1</v>
-      </c>
-      <c r="K16" s="9"/>
-    </row>
-    <row r="17" spans="1:11" ht="15.75" thickBot="1">
+    </row>
+    <row r="17" spans="1:9" ht="15" thickBot="1">
       <c r="A17" s="6">
         <v>15</v>
       </c>
-      <c r="B17" s="78"/>
-      <c r="C17" s="45" t="s">
+      <c r="B17" s="77"/>
+      <c r="C17" s="39" t="s">
+        <v>205</v>
+      </c>
+      <c r="D17" s="48" t="s">
         <v>206</v>
       </c>
-      <c r="D17" s="54" t="s">
+      <c r="E17" s="45" t="s">
+        <v>34</v>
+      </c>
+      <c r="F17" s="45" t="s">
         <v>207</v>
       </c>
-      <c r="E17" s="51" t="s">
-        <v>35</v>
-      </c>
-      <c r="F17" s="51" t="s">
-        <v>208</v>
-      </c>
-      <c r="G17" s="27" t="s">
+      <c r="G17" s="25" t="s">
+        <v>210</v>
+      </c>
+      <c r="H17" s="26" t="s">
         <v>211</v>
       </c>
-      <c r="H17" s="40" t="s">
-        <v>212</v>
-      </c>
-      <c r="I17" s="26">
+      <c r="I17" s="24">
         <v>50</v>
       </c>
-      <c r="J17" s="91">
-        <v>1</v>
-      </c>
-      <c r="K17" s="9"/>
-    </row>
-    <row r="18" spans="1:11" ht="26.25" thickBot="1">
+    </row>
+    <row r="18" spans="1:9" ht="28.2" thickBot="1">
       <c r="A18" s="6">
         <v>16</v>
       </c>
-      <c r="B18" s="79" t="s">
-        <v>149</v>
-      </c>
-      <c r="C18" s="57" t="s">
+      <c r="B18" s="81" t="s">
+        <v>148</v>
+      </c>
+      <c r="C18" s="50" t="s">
+        <v>145</v>
+      </c>
+      <c r="D18" s="47" t="s">
         <v>146</v>
       </c>
-      <c r="D18" s="53" t="s">
+      <c r="E18" s="13" t="s">
+        <v>160</v>
+      </c>
+      <c r="F18" s="13" t="s">
         <v>147</v>
       </c>
-      <c r="E18" s="31" t="s">
+      <c r="G18" s="12" t="s">
         <v>161</v>
       </c>
-      <c r="F18" s="31" t="s">
-        <v>148</v>
-      </c>
-      <c r="G18" s="14" t="s">
-        <v>162</v>
-      </c>
-      <c r="H18" s="31" t="s">
-        <v>16</v>
-      </c>
-      <c r="I18" s="13">
+      <c r="H18" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="I18" s="11">
         <v>30</v>
       </c>
-      <c r="J18" s="89">
-        <v>1</v>
-      </c>
-      <c r="K18" s="9"/>
-    </row>
-    <row r="19" spans="1:11" ht="15.75" thickBot="1">
+    </row>
+    <row r="19" spans="1:9" ht="15" thickBot="1">
       <c r="A19" s="6">
         <v>17</v>
       </c>
-      <c r="B19" s="80"/>
-      <c r="C19" s="58" t="s">
+      <c r="B19" s="82"/>
+      <c r="C19" s="51" t="s">
+        <v>178</v>
+      </c>
+      <c r="D19" s="48" t="s">
         <v>179</v>
       </c>
-      <c r="D19" s="54" t="s">
+      <c r="E19" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="F19" s="26" t="s">
         <v>180</v>
       </c>
-      <c r="E19" s="40" t="s">
-        <v>22</v>
-      </c>
-      <c r="F19" s="40" t="s">
-        <v>181</v>
-      </c>
-      <c r="G19" s="23" t="s">
-        <v>239</v>
-      </c>
-      <c r="H19" s="40" t="s">
-        <v>16</v>
-      </c>
-      <c r="I19" s="26">
+      <c r="G19" s="21" t="s">
+        <v>238</v>
+      </c>
+      <c r="H19" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="I19" s="24">
         <v>50</v>
       </c>
-      <c r="J19" s="91">
-        <v>2</v>
-      </c>
-      <c r="K19" s="9"/>
-    </row>
-    <row r="20" spans="1:11" ht="15.75" thickBot="1">
+    </row>
+    <row r="20" spans="1:9" ht="15" thickBot="1">
       <c r="A20" s="6">
         <v>18</v>
       </c>
-      <c r="B20" s="83" t="s">
-        <v>154</v>
-      </c>
-      <c r="C20" s="30" t="s">
+      <c r="B20" s="78" t="s">
+        <v>153</v>
+      </c>
+      <c r="C20" s="28" t="s">
+        <v>149</v>
+      </c>
+      <c r="D20" s="47" t="s">
         <v>150</v>
       </c>
-      <c r="D20" s="53" t="s">
+      <c r="E20" s="29" t="s">
         <v>151</v>
       </c>
-      <c r="E20" s="32" t="s">
+      <c r="F20" s="29" t="s">
         <v>152</v>
       </c>
-      <c r="F20" s="32" t="s">
-        <v>153</v>
-      </c>
-      <c r="G20" s="14" t="s">
-        <v>165</v>
-      </c>
-      <c r="H20" s="31" t="s">
-        <v>16</v>
-      </c>
-      <c r="I20" s="13">
+      <c r="G20" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="H20" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="I20" s="11">
         <v>50</v>
       </c>
-      <c r="J20" s="89">
-        <v>1</v>
-      </c>
-      <c r="K20" s="9"/>
-    </row>
-    <row r="21" spans="1:11" ht="15.75" thickBot="1">
+    </row>
+    <row r="21" spans="1:9" ht="15" thickBot="1">
       <c r="A21" s="6">
         <v>19</v>
       </c>
-      <c r="B21" s="81"/>
-      <c r="C21" s="33" t="s">
+      <c r="B21" s="73"/>
+      <c r="C21" s="30" t="s">
+        <v>185</v>
+      </c>
+      <c r="D21" s="36" t="s">
         <v>186</v>
       </c>
-      <c r="D21" s="42" t="s">
+      <c r="E21" s="31" t="s">
+        <v>151</v>
+      </c>
+      <c r="F21" s="31" t="s">
         <v>187</v>
       </c>
-      <c r="E21" s="35" t="s">
-        <v>152</v>
-      </c>
-      <c r="F21" s="35" t="s">
-        <v>188</v>
-      </c>
-      <c r="G21" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="H21" s="34" t="s">
-        <v>167</v>
-      </c>
-      <c r="I21" s="20">
+      <c r="G21" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="H21" s="17" t="s">
+        <v>166</v>
+      </c>
+      <c r="I21" s="18">
         <v>45</v>
       </c>
-      <c r="J21" s="90">
-        <v>2</v>
-      </c>
-      <c r="K21" s="9"/>
-    </row>
-    <row r="22" spans="1:11" ht="15.75" thickBot="1">
+    </row>
+    <row r="22" spans="1:9" ht="15" thickBot="1">
       <c r="A22" s="6">
         <v>20</v>
       </c>
-      <c r="B22" s="81"/>
-      <c r="C22" s="33" t="s">
+      <c r="B22" s="73"/>
+      <c r="C22" s="30" t="s">
+        <v>188</v>
+      </c>
+      <c r="D22" s="36" t="s">
         <v>189</v>
       </c>
-      <c r="D22" s="42" t="s">
+      <c r="E22" s="31" t="s">
         <v>190</v>
       </c>
-      <c r="E22" s="35" t="s">
+      <c r="F22" s="31" t="s">
         <v>191</v>
       </c>
-      <c r="F22" s="35" t="s">
+      <c r="G22" s="15" t="s">
         <v>192</v>
       </c>
-      <c r="G22" s="17" t="s">
-        <v>193</v>
-      </c>
-      <c r="H22" s="34" t="s">
-        <v>167</v>
-      </c>
-      <c r="I22" s="20">
+      <c r="H22" s="17" t="s">
+        <v>166</v>
+      </c>
+      <c r="I22" s="18">
         <v>50</v>
       </c>
-      <c r="J22" s="90">
-        <v>2</v>
-      </c>
-      <c r="K22" s="9"/>
-    </row>
-    <row r="23" spans="1:11" ht="15.75" thickBot="1">
+    </row>
+    <row r="23" spans="1:9" ht="15" thickBot="1">
       <c r="A23" s="6">
         <v>21</v>
       </c>
-      <c r="B23" s="82"/>
-      <c r="C23" s="45" t="s">
+      <c r="B23" s="74"/>
+      <c r="C23" s="39" t="s">
+        <v>212</v>
+      </c>
+      <c r="D23" s="48" t="s">
         <v>213</v>
       </c>
-      <c r="D23" s="54" t="s">
+      <c r="E23" s="45" t="s">
+        <v>21</v>
+      </c>
+      <c r="F23" s="45" t="s">
         <v>214</v>
       </c>
-      <c r="E23" s="51" t="s">
-        <v>22</v>
-      </c>
-      <c r="F23" s="51" t="s">
+      <c r="G23" s="25" t="s">
         <v>215</v>
       </c>
-      <c r="G23" s="27" t="s">
-        <v>216</v>
-      </c>
-      <c r="H23" s="40" t="s">
-        <v>167</v>
-      </c>
-      <c r="I23" s="26">
+      <c r="H23" s="26" t="s">
+        <v>166</v>
+      </c>
+      <c r="I23" s="24">
         <v>30</v>
       </c>
-      <c r="J23" s="91">
-        <v>1</v>
-      </c>
-      <c r="K23" s="9"/>
-    </row>
-    <row r="24" spans="1:11" ht="26.25" thickBot="1">
+    </row>
+    <row r="24" spans="1:9" ht="28.2" thickBot="1">
       <c r="A24" s="6">
         <v>22</v>
       </c>
-      <c r="B24" s="64" t="s">
-        <v>62</v>
-      </c>
-      <c r="C24" s="66" t="s">
+      <c r="B24" s="57" t="s">
+        <v>61</v>
+      </c>
+      <c r="C24" s="59" t="s">
+        <v>58</v>
+      </c>
+      <c r="D24" s="67" t="s">
         <v>59</v>
       </c>
-      <c r="D24" s="85" t="s">
+      <c r="E24" s="60" t="s">
+        <v>21</v>
+      </c>
+      <c r="F24" s="60" t="s">
         <v>60</v>
       </c>
-      <c r="E24" s="67" t="s">
-        <v>22</v>
-      </c>
-      <c r="F24" s="67" t="s">
-        <v>61</v>
-      </c>
-      <c r="G24" s="68" t="s">
-        <v>115</v>
-      </c>
-      <c r="H24" s="67" t="s">
-        <v>16</v>
-      </c>
-      <c r="I24" s="67">
+      <c r="G24" s="61" t="s">
+        <v>114</v>
+      </c>
+      <c r="H24" s="60" t="s">
+        <v>15</v>
+      </c>
+      <c r="I24" s="60">
         <v>162</v>
       </c>
-      <c r="J24" s="92">
-        <v>8</v>
-      </c>
-      <c r="K24" s="9"/>
-    </row>
-    <row r="25" spans="1:11" ht="26.25" thickBot="1">
+    </row>
+    <row r="25" spans="1:9" ht="28.2" thickBot="1">
       <c r="A25" s="6">
         <v>23</v>
       </c>
-      <c r="B25" s="63" t="s">
+      <c r="B25" s="56" t="s">
+        <v>19</v>
+      </c>
+      <c r="C25" s="38" t="s">
+        <v>62</v>
+      </c>
+      <c r="D25" s="68" t="s">
         <v>20</v>
       </c>
-      <c r="C25" s="44" t="s">
+      <c r="E25" s="32" t="s">
+        <v>21</v>
+      </c>
+      <c r="F25" s="32" t="s">
         <v>63</v>
       </c>
-      <c r="D25" s="86" t="s">
-        <v>21</v>
-      </c>
-      <c r="E25" s="36" t="s">
-        <v>22</v>
-      </c>
-      <c r="F25" s="36" t="s">
-        <v>64</v>
-      </c>
-      <c r="G25" s="23" t="s">
-        <v>103</v>
-      </c>
-      <c r="H25" s="56" t="s">
-        <v>16</v>
-      </c>
-      <c r="I25" s="56">
+      <c r="G25" s="21" t="s">
+        <v>102</v>
+      </c>
+      <c r="H25" s="32" t="s">
+        <v>15</v>
+      </c>
+      <c r="I25" s="32">
         <v>30</v>
       </c>
-      <c r="J25" s="93">
-        <v>1</v>
-      </c>
-      <c r="K25" s="9"/>
-    </row>
-    <row r="26" spans="1:11" ht="26.25" thickBot="1">
+    </row>
+    <row r="26" spans="1:9" ht="28.2" thickBot="1">
       <c r="A26" s="6">
         <v>24</v>
       </c>
-      <c r="B26" s="76" t="s">
+      <c r="B26" s="75" t="s">
+        <v>24</v>
+      </c>
+      <c r="C26" s="33" t="s">
+        <v>64</v>
+      </c>
+      <c r="D26" s="52" t="s">
         <v>25</v>
       </c>
-      <c r="C26" s="37" t="s">
+      <c r="E26" s="23" t="s">
+        <v>21</v>
+      </c>
+      <c r="F26" s="23" t="s">
         <v>65</v>
       </c>
-      <c r="D26" s="59" t="s">
-        <v>26</v>
-      </c>
-      <c r="E26" s="38" t="s">
+      <c r="G26" s="22" t="s">
+        <v>103</v>
+      </c>
+      <c r="H26" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="I26" s="23">
         <v>22</v>
       </c>
-      <c r="F26" s="38" t="s">
-        <v>66</v>
-      </c>
-      <c r="G26" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="H26" s="25" t="s">
-        <v>16</v>
-      </c>
-      <c r="I26" s="25">
-        <v>22</v>
-      </c>
-      <c r="J26" s="94">
-        <v>1</v>
-      </c>
-      <c r="K26" s="9"/>
-    </row>
-    <row r="27" spans="1:11" ht="26.25" thickBot="1">
+    </row>
+    <row r="27" spans="1:9" ht="28.2" thickBot="1">
       <c r="A27" s="6">
         <v>25</v>
       </c>
-      <c r="B27" s="77"/>
-      <c r="C27" s="41" t="s">
+      <c r="B27" s="76"/>
+      <c r="C27" s="35" t="s">
+        <v>66</v>
+      </c>
+      <c r="D27" s="46" t="s">
         <v>67</v>
       </c>
-      <c r="D27" s="52" t="s">
+      <c r="E27" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="F27" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="E27" s="34" t="s">
-        <v>22</v>
-      </c>
-      <c r="F27" s="34" t="s">
-        <v>69</v>
-      </c>
-      <c r="G27" s="17" t="s">
-        <v>105</v>
-      </c>
-      <c r="H27" s="19" t="s">
-        <v>16</v>
-      </c>
-      <c r="I27" s="19">
+      <c r="G27" s="15" t="s">
+        <v>104</v>
+      </c>
+      <c r="H27" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="I27" s="17">
         <v>45</v>
       </c>
-      <c r="J27" s="95">
-        <v>2</v>
-      </c>
-      <c r="K27" s="9"/>
-    </row>
-    <row r="28" spans="1:11" ht="26.25" thickBot="1">
+    </row>
+    <row r="28" spans="1:9" ht="28.2" thickBot="1">
       <c r="A28" s="6">
         <v>26</v>
       </c>
-      <c r="B28" s="78"/>
-      <c r="C28" s="39" t="s">
+      <c r="B28" s="77"/>
+      <c r="C28" s="34" t="s">
+        <v>129</v>
+      </c>
+      <c r="D28" s="54" t="s">
         <v>130</v>
       </c>
-      <c r="D28" s="61" t="s">
+      <c r="E28" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="F28" s="26" t="s">
         <v>131</v>
       </c>
-      <c r="E28" s="40" t="s">
-        <v>22</v>
-      </c>
-      <c r="F28" s="40" t="s">
-        <v>132</v>
-      </c>
-      <c r="G28" s="27" t="s">
+      <c r="G28" s="25" t="s">
+        <v>165</v>
+      </c>
+      <c r="H28" s="26" t="s">
         <v>166</v>
       </c>
-      <c r="H28" s="28" t="s">
-        <v>167</v>
-      </c>
-      <c r="I28" s="28">
+      <c r="I28" s="26">
         <v>25</v>
       </c>
-      <c r="J28" s="96">
-        <v>1</v>
-      </c>
-      <c r="K28" s="9"/>
-    </row>
-    <row r="29" spans="1:11" ht="15.75" thickBot="1">
+    </row>
+    <row r="29" spans="1:9" ht="15" thickBot="1">
       <c r="A29" s="6">
         <v>27</v>
       </c>
-      <c r="B29" s="76" t="s">
+      <c r="B29" s="75" t="s">
+        <v>16</v>
+      </c>
+      <c r="C29" s="33" t="s">
+        <v>69</v>
+      </c>
+      <c r="D29" s="52" t="s">
+        <v>132</v>
+      </c>
+      <c r="E29" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="C29" s="37" t="s">
-        <v>70</v>
-      </c>
-      <c r="D29" s="59" t="s">
-        <v>133</v>
-      </c>
-      <c r="E29" s="31" t="s">
-        <v>18</v>
-      </c>
-      <c r="F29" s="53" t="s">
+      <c r="F29" s="47" t="s">
+        <v>105</v>
+      </c>
+      <c r="G29" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="G29" s="14" t="s">
-        <v>107</v>
-      </c>
-      <c r="H29" s="31" t="s">
-        <v>73</v>
-      </c>
-      <c r="I29" s="60">
+      <c r="H29" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="I29" s="53">
         <v>100</v>
       </c>
-      <c r="J29" s="97">
-        <v>3</v>
-      </c>
-      <c r="K29" s="9"/>
-    </row>
-    <row r="30" spans="1:11" ht="15.75" thickBot="1">
+    </row>
+    <row r="30" spans="1:9" ht="15" thickBot="1">
       <c r="A30" s="6">
         <v>28</v>
       </c>
-      <c r="B30" s="77"/>
-      <c r="C30" s="41" t="s">
+      <c r="B30" s="76"/>
+      <c r="C30" s="35" t="s">
+        <v>217</v>
+      </c>
+      <c r="D30" s="46" t="s">
+        <v>133</v>
+      </c>
+      <c r="E30" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="F30" s="17" t="s">
         <v>218</v>
       </c>
-      <c r="D30" s="52" t="s">
-        <v>134</v>
-      </c>
-      <c r="E30" s="34" t="s">
-        <v>18</v>
-      </c>
-      <c r="F30" s="34" t="s">
+      <c r="G30" s="15" t="s">
         <v>219</v>
       </c>
-      <c r="G30" s="17" t="s">
-        <v>220</v>
-      </c>
-      <c r="H30" s="34" t="s">
-        <v>217</v>
-      </c>
-      <c r="I30" s="43">
+      <c r="H30" s="17" t="s">
+        <v>216</v>
+      </c>
+      <c r="I30" s="37">
         <v>100</v>
       </c>
-      <c r="J30" s="98">
-        <v>1</v>
-      </c>
-      <c r="K30" s="9"/>
-    </row>
-    <row r="31" spans="1:11" ht="15.75" thickBot="1">
+    </row>
+    <row r="31" spans="1:9" ht="15" thickBot="1">
       <c r="A31" s="6">
         <v>29</v>
       </c>
-      <c r="B31" s="77"/>
-      <c r="C31" s="41" t="s">
+      <c r="B31" s="76"/>
+      <c r="C31" s="35" t="s">
+        <v>134</v>
+      </c>
+      <c r="D31" s="46" t="s">
         <v>135</v>
       </c>
-      <c r="D31" s="52" t="s">
+      <c r="E31" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="F31" s="17" t="s">
         <v>136</v>
       </c>
-      <c r="E31" s="34" t="s">
-        <v>18</v>
-      </c>
-      <c r="F31" s="34" t="s">
+      <c r="G31" s="15" t="s">
+        <v>167</v>
+      </c>
+      <c r="H31" s="17" t="s">
         <v>137</v>
       </c>
-      <c r="G31" s="17" t="s">
-        <v>168</v>
-      </c>
-      <c r="H31" s="34" t="s">
-        <v>138</v>
-      </c>
-      <c r="I31" s="43">
+      <c r="I31" s="37">
         <v>100</v>
       </c>
-      <c r="J31" s="98">
-        <v>1</v>
-      </c>
-      <c r="K31" s="9"/>
-    </row>
-    <row r="32" spans="1:11" ht="15.75" thickBot="1">
+    </row>
+    <row r="32" spans="1:9" ht="15" thickBot="1">
       <c r="A32" s="6">
         <v>30</v>
       </c>
-      <c r="B32" s="77"/>
-      <c r="C32" s="41" t="s">
+      <c r="B32" s="76"/>
+      <c r="C32" s="35" t="s">
+        <v>193</v>
+      </c>
+      <c r="D32" s="46" t="s">
         <v>194</v>
       </c>
-      <c r="D32" s="52" t="s">
+      <c r="E32" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="F32" s="17" t="s">
         <v>195</v>
       </c>
-      <c r="E32" s="34" t="s">
-        <v>18</v>
-      </c>
-      <c r="F32" s="34" t="s">
+      <c r="G32" s="15" t="s">
         <v>196</v>
       </c>
-      <c r="G32" s="17" t="s">
+      <c r="H32" s="17" t="s">
         <v>197</v>
       </c>
-      <c r="H32" s="34" t="s">
-        <v>198</v>
-      </c>
-      <c r="I32" s="43">
+      <c r="I32" s="37">
         <v>100</v>
       </c>
-      <c r="J32" s="98">
-        <v>4</v>
-      </c>
-      <c r="K32" s="9"/>
-    </row>
-    <row r="33" spans="1:11" ht="15.75" thickBot="1">
+    </row>
+    <row r="33" spans="1:9" ht="15" thickBot="1">
       <c r="A33" s="6">
         <v>31</v>
       </c>
-      <c r="B33" s="78"/>
-      <c r="C33" s="39" t="s">
+      <c r="B33" s="77"/>
+      <c r="C33" s="34" t="s">
+        <v>70</v>
+      </c>
+      <c r="D33" s="54" t="s">
+        <v>227</v>
+      </c>
+      <c r="E33" s="26" t="s">
+        <v>17</v>
+      </c>
+      <c r="F33" s="26" t="s">
         <v>71</v>
       </c>
-      <c r="D33" s="61" t="s">
-        <v>228</v>
-      </c>
-      <c r="E33" s="40" t="s">
+      <c r="G33" s="25" t="s">
+        <v>107</v>
+      </c>
+      <c r="H33" s="26" t="s">
         <v>18</v>
       </c>
-      <c r="F33" s="40" t="s">
-        <v>72</v>
-      </c>
-      <c r="G33" s="27" t="s">
-        <v>108</v>
-      </c>
-      <c r="H33" s="40" t="s">
-        <v>19</v>
-      </c>
-      <c r="I33" s="62">
+      <c r="I33" s="55">
         <v>100</v>
       </c>
-      <c r="J33" s="99">
-        <v>2</v>
-      </c>
-      <c r="K33" s="9"/>
-    </row>
-    <row r="34" spans="1:11" ht="15.75" thickBot="1">
+    </row>
+    <row r="34" spans="1:9" ht="15" thickBot="1">
       <c r="A34" s="6">
         <v>32</v>
       </c>
-      <c r="B34" s="76" t="s">
-        <v>90</v>
-      </c>
-      <c r="C34" s="37" t="s">
+      <c r="B34" s="75" t="s">
+        <v>89</v>
+      </c>
+      <c r="C34" s="33" t="s">
+        <v>73</v>
+      </c>
+      <c r="D34" s="52" t="s">
         <v>74</v>
       </c>
-      <c r="D34" s="59" t="s">
+      <c r="E34" s="13" t="s">
         <v>75</v>
       </c>
-      <c r="E34" s="31" t="s">
+      <c r="F34" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="F34" s="31" t="s">
-        <v>77</v>
-      </c>
-      <c r="G34" s="84" t="s">
-        <v>30</v>
-      </c>
-      <c r="H34" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="I34" s="15">
+      <c r="G34" s="66" t="s">
+        <v>29</v>
+      </c>
+      <c r="H34" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="I34" s="13">
         <v>42</v>
       </c>
-      <c r="J34" s="89">
-        <v>2</v>
-      </c>
-      <c r="K34" s="9"/>
-    </row>
-    <row r="35" spans="1:11" ht="26.25" thickBot="1">
+    </row>
+    <row r="35" spans="1:9" ht="28.2" thickBot="1">
       <c r="A35" s="6">
         <v>33</v>
       </c>
-      <c r="B35" s="77"/>
-      <c r="C35" s="41" t="s">
+      <c r="B35" s="76"/>
+      <c r="C35" s="35" t="s">
+        <v>77</v>
+      </c>
+      <c r="D35" s="46" t="s">
+        <v>23</v>
+      </c>
+      <c r="E35" s="17" t="s">
         <v>78</v>
       </c>
-      <c r="D35" s="52" t="s">
-        <v>24</v>
-      </c>
-      <c r="E35" s="34" t="s">
+      <c r="F35" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="F35" s="34" t="s">
-        <v>80</v>
-      </c>
-      <c r="G35" s="18" t="s">
-        <v>109</v>
-      </c>
-      <c r="H35" s="19" t="s">
-        <v>16</v>
-      </c>
-      <c r="I35" s="18">
+      <c r="G35" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="H35" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="I35" s="16">
         <v>21</v>
       </c>
-      <c r="J35" s="90">
-        <v>1</v>
-      </c>
-      <c r="K35" s="9"/>
-    </row>
-    <row r="36" spans="1:11" ht="15.75" thickBot="1">
+    </row>
+    <row r="36" spans="1:9" ht="15" thickBot="1">
       <c r="A36" s="6">
         <v>34</v>
       </c>
-      <c r="B36" s="77"/>
-      <c r="C36" s="41" t="s">
+      <c r="B36" s="76"/>
+      <c r="C36" s="35" t="s">
+        <v>80</v>
+      </c>
+      <c r="D36" s="46" t="s">
+        <v>22</v>
+      </c>
+      <c r="E36" s="17" t="s">
         <v>81</v>
       </c>
-      <c r="D36" s="52" t="s">
-        <v>23</v>
-      </c>
-      <c r="E36" s="34" t="s">
+      <c r="F36" s="17" t="s">
         <v>82</v>
       </c>
-      <c r="F36" s="34" t="s">
-        <v>83</v>
-      </c>
-      <c r="G36" s="20" t="s">
-        <v>16</v>
-      </c>
-      <c r="H36" s="19" t="s">
-        <v>16</v>
-      </c>
-      <c r="I36" s="20">
+      <c r="G36" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="H36" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="I36" s="18">
         <v>21</v>
       </c>
-      <c r="J36" s="90">
-        <v>1</v>
-      </c>
-      <c r="K36" s="9"/>
-    </row>
-    <row r="37" spans="1:11" ht="15.75" thickBot="1">
+    </row>
+    <row r="37" spans="1:9" ht="15" thickBot="1">
       <c r="A37" s="6">
         <v>35</v>
       </c>
-      <c r="B37" s="77"/>
-      <c r="C37" s="69" t="s">
+      <c r="B37" s="76"/>
+      <c r="C37" s="35" t="s">
+        <v>83</v>
+      </c>
+      <c r="D37" s="46" t="s">
         <v>84</v>
       </c>
-      <c r="D37" s="52" t="s">
+      <c r="E37" s="17" t="s">
+        <v>109</v>
+      </c>
+      <c r="F37" s="17" t="s">
         <v>85</v>
       </c>
-      <c r="E37" s="19" t="s">
-        <v>110</v>
-      </c>
-      <c r="F37" s="19" t="s">
-        <v>86</v>
-      </c>
-      <c r="G37" s="20" t="s">
-        <v>16</v>
-      </c>
-      <c r="H37" s="19" t="s">
-        <v>16</v>
-      </c>
-      <c r="I37" s="20">
+      <c r="G37" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="H37" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="I37" s="18">
         <v>41</v>
       </c>
-      <c r="J37" s="100">
-        <v>2</v>
-      </c>
-      <c r="K37" s="9"/>
-    </row>
-    <row r="38" spans="1:11" ht="15.75" thickBot="1">
+    </row>
+    <row r="38" spans="1:9" ht="15" thickBot="1">
       <c r="A38" s="6">
         <v>36</v>
       </c>
-      <c r="B38" s="77"/>
-      <c r="C38" s="41" t="s">
+      <c r="B38" s="76"/>
+      <c r="C38" s="35" t="s">
+        <v>138</v>
+      </c>
+      <c r="D38" s="46" t="s">
         <v>139</v>
       </c>
-      <c r="D38" s="52" t="s">
+      <c r="E38" s="17" t="s">
+        <v>168</v>
+      </c>
+      <c r="F38" s="17" t="s">
         <v>140</v>
       </c>
-      <c r="E38" s="34" t="s">
+      <c r="G38" s="18" t="s">
         <v>169</v>
       </c>
-      <c r="F38" s="34" t="s">
-        <v>141</v>
-      </c>
-      <c r="G38" s="20" t="s">
-        <v>170</v>
-      </c>
-      <c r="H38" s="19" t="s">
-        <v>16</v>
-      </c>
-      <c r="I38" s="20">
+      <c r="H38" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="I38" s="18">
         <v>21</v>
       </c>
-      <c r="J38" s="90">
-        <v>1</v>
-      </c>
-      <c r="K38" s="9"/>
-    </row>
-    <row r="39" spans="1:11" ht="15.75" thickBot="1">
+    </row>
+    <row r="39" spans="1:9" ht="15" thickBot="1">
       <c r="A39" s="6">
         <v>37</v>
       </c>
-      <c r="B39" s="77"/>
-      <c r="C39" s="41" t="s">
+      <c r="B39" s="76"/>
+      <c r="C39" s="35" t="s">
+        <v>141</v>
+      </c>
+      <c r="D39" s="46" t="s">
         <v>142</v>
       </c>
-      <c r="D39" s="52" t="s">
+      <c r="E39" s="17" t="s">
         <v>143</v>
       </c>
-      <c r="E39" s="34" t="s">
+      <c r="F39" s="17" t="s">
         <v>144</v>
       </c>
-      <c r="F39" s="34" t="s">
-        <v>145</v>
-      </c>
-      <c r="G39" s="20" t="s">
-        <v>171</v>
-      </c>
-      <c r="H39" s="19" t="s">
-        <v>16</v>
-      </c>
-      <c r="I39" s="20">
+      <c r="G39" s="18" t="s">
+        <v>170</v>
+      </c>
+      <c r="H39" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="I39" s="18">
         <v>21</v>
       </c>
-      <c r="J39" s="90">
-        <v>1</v>
-      </c>
-      <c r="K39" s="9"/>
-    </row>
-    <row r="40" spans="1:11" ht="15.75" thickBot="1">
+    </row>
+    <row r="40" spans="1:9" ht="15" thickBot="1">
       <c r="A40" s="6">
         <v>38</v>
       </c>
-      <c r="B40" s="77"/>
-      <c r="C40" s="41" t="s">
+      <c r="B40" s="76"/>
+      <c r="C40" s="35" t="s">
+        <v>220</v>
+      </c>
+      <c r="D40" s="46" t="s">
         <v>221</v>
       </c>
-      <c r="D40" s="52" t="s">
+      <c r="E40" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="F40" s="17" t="s">
         <v>222</v>
       </c>
-      <c r="E40" s="34" t="s">
+      <c r="G40" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="H40" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="I40" s="18">
         <v>22</v>
       </c>
-      <c r="F40" s="34" t="s">
-        <v>223</v>
-      </c>
-      <c r="G40" s="20" t="s">
-        <v>31</v>
-      </c>
-      <c r="H40" s="19" t="s">
-        <v>16</v>
-      </c>
-      <c r="I40" s="20">
-        <v>22</v>
-      </c>
-      <c r="J40" s="90">
-        <v>1</v>
-      </c>
-      <c r="K40" s="9"/>
-    </row>
-    <row r="41" spans="1:11" ht="15.75" thickBot="1">
+    </row>
+    <row r="41" spans="1:9" ht="15" thickBot="1">
       <c r="A41" s="6">
         <v>39</v>
       </c>
-      <c r="B41" s="77"/>
-      <c r="C41" s="44" t="s">
+      <c r="B41" s="76"/>
+      <c r="C41" s="38" t="s">
+        <v>230</v>
+      </c>
+      <c r="D41" s="68" t="s">
+        <v>228</v>
+      </c>
+      <c r="E41" s="32" t="s">
         <v>231</v>
       </c>
-      <c r="D41" s="86" t="s">
-        <v>229</v>
-      </c>
-      <c r="E41" s="36" t="s">
+      <c r="F41" s="2" t="s">
         <v>232</v>
       </c>
-      <c r="F41" s="101" t="s">
-        <v>233</v>
-      </c>
-      <c r="G41" s="22" t="s">
+      <c r="G41" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="H41" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="I41" s="20">
         <v>30</v>
       </c>
-      <c r="H41" s="19" t="s">
-        <v>16</v>
-      </c>
-      <c r="I41" s="22">
-        <v>30</v>
-      </c>
-      <c r="J41" s="102">
-        <v>1</v>
-      </c>
-      <c r="K41" s="9"/>
-    </row>
-    <row r="42" spans="1:11" ht="26.25" thickBot="1">
+    </row>
+    <row r="42" spans="1:9" ht="28.2" thickBot="1">
       <c r="A42" s="6">
         <v>40</v>
       </c>
-      <c r="B42" s="78"/>
-      <c r="C42" s="39" t="s">
+      <c r="B42" s="77"/>
+      <c r="C42" s="34" t="s">
+        <v>86</v>
+      </c>
+      <c r="D42" s="54" t="s">
         <v>87</v>
       </c>
-      <c r="D42" s="61" t="s">
+      <c r="E42" s="26" t="s">
+        <v>110</v>
+      </c>
+      <c r="F42" s="26" t="s">
         <v>88</v>
       </c>
-      <c r="E42" s="40" t="s">
+      <c r="G42" s="26" t="s">
         <v>111</v>
       </c>
-      <c r="F42" s="40" t="s">
-        <v>89</v>
-      </c>
-      <c r="G42" s="28" t="s">
-        <v>112</v>
-      </c>
-      <c r="H42" s="28" t="s">
-        <v>16</v>
-      </c>
-      <c r="I42" s="26">
+      <c r="H42" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="I42" s="24">
         <v>30</v>
       </c>
-      <c r="J42" s="91">
-        <v>1</v>
-      </c>
-      <c r="K42" s="9"/>
-    </row>
-    <row r="43" spans="1:11" ht="15.75" thickBot="1">
+    </row>
+    <row r="43" spans="1:9" ht="15" thickBot="1">
       <c r="A43" s="6">
         <v>41</v>
       </c>
-      <c r="B43" s="76" t="s">
-        <v>94</v>
-      </c>
-      <c r="C43" s="37" t="s">
+      <c r="B43" s="75" t="s">
+        <v>93</v>
+      </c>
+      <c r="C43" s="33" t="s">
+        <v>90</v>
+      </c>
+      <c r="D43" s="52" t="s">
+        <v>31</v>
+      </c>
+      <c r="E43" s="71" t="s">
+        <v>21</v>
+      </c>
+      <c r="F43" s="58" t="s">
         <v>91</v>
       </c>
-      <c r="D43" s="59" t="s">
-        <v>32</v>
-      </c>
-      <c r="E43" s="110" t="s">
-        <v>22</v>
-      </c>
-      <c r="F43" s="65" t="s">
-        <v>92</v>
-      </c>
-      <c r="G43" s="16" t="s">
-        <v>113</v>
-      </c>
-      <c r="H43" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="I43" s="29">
+      <c r="G43" s="14" t="s">
+        <v>112</v>
+      </c>
+      <c r="H43" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="I43" s="27">
         <v>50</v>
       </c>
-      <c r="J43" s="103">
-        <v>1</v>
-      </c>
-      <c r="K43" s="9"/>
-    </row>
-    <row r="44" spans="1:11" ht="26.25" thickBot="1">
+    </row>
+    <row r="44" spans="1:9" ht="28.2" thickBot="1">
       <c r="A44" s="6">
         <v>42</v>
       </c>
-      <c r="B44" s="77"/>
-      <c r="C44" s="41" t="s">
+      <c r="B44" s="76"/>
+      <c r="C44" s="35" t="s">
+        <v>235</v>
+      </c>
+      <c r="D44" s="46" t="s">
+        <v>32</v>
+      </c>
+      <c r="E44" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="F44" s="17" t="s">
         <v>236</v>
       </c>
-      <c r="D44" s="52" t="s">
-        <v>33</v>
-      </c>
-      <c r="E44" s="34" t="s">
-        <v>22</v>
-      </c>
-      <c r="F44" s="34" t="s">
+      <c r="G44" s="17" t="s">
         <v>237</v>
       </c>
-      <c r="G44" s="19" t="s">
-        <v>238</v>
-      </c>
-      <c r="H44" s="19" t="s">
-        <v>16</v>
-      </c>
-      <c r="I44" s="19">
+      <c r="H44" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="I44" s="17">
         <v>30</v>
       </c>
-      <c r="J44" s="104">
-        <v>1</v>
-      </c>
-      <c r="K44" s="9"/>
-    </row>
-    <row r="45" spans="1:11" ht="15.75" thickBot="1">
+    </row>
+    <row r="45" spans="1:9" ht="15" thickBot="1">
       <c r="A45" s="6">
         <v>43</v>
       </c>
-      <c r="B45" s="77"/>
-      <c r="C45" s="41" t="s">
-        <v>93</v>
-      </c>
-      <c r="D45" s="52" t="s">
-        <v>27</v>
-      </c>
-      <c r="E45" s="34" t="s">
-        <v>22</v>
-      </c>
-      <c r="F45" s="19" t="s">
-        <v>116</v>
-      </c>
-      <c r="G45" s="19" t="s">
-        <v>114</v>
-      </c>
-      <c r="H45" s="19" t="s">
-        <v>16</v>
-      </c>
-      <c r="I45" s="19">
+      <c r="B45" s="76"/>
+      <c r="C45" s="35" t="s">
+        <v>92</v>
+      </c>
+      <c r="D45" s="46" t="s">
+        <v>26</v>
+      </c>
+      <c r="E45" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="F45" s="17" t="s">
+        <v>115</v>
+      </c>
+      <c r="G45" s="17" t="s">
+        <v>113</v>
+      </c>
+      <c r="H45" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="I45" s="17">
         <v>50</v>
       </c>
-      <c r="J45" s="104">
-        <v>1</v>
-      </c>
-      <c r="K45" s="9"/>
-    </row>
-    <row r="46" spans="1:11" ht="15.75" thickBot="1">
+    </row>
+    <row r="46" spans="1:9" ht="15" thickBot="1">
       <c r="A46" s="6">
         <v>44</v>
       </c>
-      <c r="B46" s="77"/>
-      <c r="C46" s="41" t="s">
+      <c r="B46" s="76"/>
+      <c r="C46" s="35" t="s">
+        <v>223</v>
+      </c>
+      <c r="D46" s="46" t="s">
         <v>224</v>
       </c>
-      <c r="D46" s="52" t="s">
+      <c r="E46" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="F46" s="17" t="s">
         <v>225</v>
       </c>
-      <c r="E46" s="34" t="s">
-        <v>22</v>
-      </c>
-      <c r="F46" s="34" t="s">
+      <c r="G46" s="17" t="s">
         <v>226</v>
       </c>
-      <c r="G46" s="19" t="s">
-        <v>227</v>
-      </c>
-      <c r="H46" s="19" t="s">
-        <v>16</v>
-      </c>
-      <c r="I46" s="19">
+      <c r="H46" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="I46" s="17">
         <v>25</v>
       </c>
-      <c r="J46" s="104">
-        <v>1</v>
-      </c>
-      <c r="K46" s="9"/>
-    </row>
-    <row r="47" spans="1:11" ht="15.75" thickBot="1">
+    </row>
+    <row r="47" spans="1:9" ht="15" thickBot="1">
       <c r="A47" s="6">
         <v>45</v>
       </c>
-      <c r="B47" s="77"/>
-      <c r="C47" s="44" t="s">
+      <c r="B47" s="76"/>
+      <c r="C47" s="38" t="s">
+        <v>233</v>
+      </c>
+      <c r="D47" s="69" t="s">
+        <v>229</v>
+      </c>
+      <c r="E47" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="F47" s="70">
+        <v>61300611121</v>
+      </c>
+      <c r="G47" s="32" t="s">
         <v>234</v>
       </c>
-      <c r="D47" s="87" t="s">
-        <v>230</v>
-      </c>
-      <c r="E47" s="34" t="s">
-        <v>22</v>
-      </c>
-      <c r="F47" s="105">
-        <v>61300611121</v>
-      </c>
-      <c r="G47" s="56" t="s">
-        <v>235</v>
-      </c>
-      <c r="H47" s="19" t="s">
-        <v>16</v>
-      </c>
-      <c r="I47" s="56">
+      <c r="H47" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="I47" s="32">
         <v>40</v>
       </c>
-      <c r="J47" s="106">
-        <v>1</v>
-      </c>
-      <c r="K47" s="9"/>
-    </row>
-    <row r="48" spans="1:11" ht="102.75" thickBot="1">
+    </row>
+    <row r="48" spans="1:9" ht="111" thickBot="1">
       <c r="A48" s="6">
         <v>46</v>
       </c>
-      <c r="B48" s="78"/>
-      <c r="C48" s="46" t="s">
+      <c r="B48" s="77"/>
+      <c r="C48" s="40" t="s">
+        <v>27</v>
+      </c>
+      <c r="D48" s="41" t="s">
+        <v>198</v>
+      </c>
+      <c r="E48" s="42" t="s">
         <v>28</v>
       </c>
-      <c r="D48" s="47" t="s">
-        <v>199</v>
-      </c>
-      <c r="E48" s="48" t="s">
-        <v>29</v>
-      </c>
-      <c r="F48" s="48" t="s">
-        <v>29</v>
-      </c>
-      <c r="G48" s="49"/>
-      <c r="H48" s="50" t="s">
-        <v>31</v>
-      </c>
-      <c r="I48" s="50" t="s">
-        <v>16</v>
-      </c>
-      <c r="J48" s="107">
-        <v>53</v>
-      </c>
-      <c r="K48" s="9"/>
-    </row>
-    <row r="49" spans="1:11" ht="26.25" thickBot="1">
+      <c r="F48" s="42" t="s">
+        <v>28</v>
+      </c>
+      <c r="G48" s="43"/>
+      <c r="H48" s="44" t="s">
+        <v>30</v>
+      </c>
+      <c r="I48" s="44" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" ht="28.2" thickBot="1">
       <c r="A49" s="6">
         <v>47</v>
       </c>
-      <c r="B49" s="81" t="s">
+      <c r="B49" s="73" t="s">
+        <v>117</v>
+      </c>
+      <c r="C49" s="62" t="s">
+        <v>201</v>
+      </c>
+      <c r="D49" s="63" t="s">
+        <v>30</v>
+      </c>
+      <c r="E49" s="63" t="s">
+        <v>30</v>
+      </c>
+      <c r="F49" s="63" t="s">
+        <v>200</v>
+      </c>
+      <c r="G49" s="63" t="s">
+        <v>114</v>
+      </c>
+      <c r="H49" s="63" t="s">
+        <v>114</v>
+      </c>
+      <c r="I49" s="63" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" ht="15" thickBot="1">
+      <c r="A50" s="72">
+        <v>48</v>
+      </c>
+      <c r="B50" s="74"/>
+      <c r="C50" s="64" t="s">
         <v>118</v>
       </c>
-      <c r="C49" s="70" t="s">
-        <v>202</v>
-      </c>
-      <c r="D49" s="71" t="s">
-        <v>31</v>
-      </c>
-      <c r="E49" s="71" t="s">
-        <v>31</v>
-      </c>
-      <c r="F49" s="71" t="s">
-        <v>201</v>
-      </c>
-      <c r="G49" s="71" t="s">
-        <v>115</v>
-      </c>
-      <c r="H49" s="71" t="s">
-        <v>115</v>
-      </c>
-      <c r="I49" s="71" t="s">
-        <v>115</v>
-      </c>
-      <c r="J49" s="108">
-        <v>1</v>
-      </c>
-      <c r="K49" s="9"/>
-    </row>
-    <row r="50" spans="1:11" ht="15.75" thickBot="1">
-      <c r="A50" s="111">
-        <v>48</v>
-      </c>
-      <c r="B50" s="82"/>
-      <c r="C50" s="72" t="s">
-        <v>119</v>
-      </c>
-      <c r="D50" s="73" t="s">
-        <v>31</v>
-      </c>
-      <c r="E50" s="73" t="s">
-        <v>31</v>
-      </c>
-      <c r="F50" s="73" t="s">
-        <v>119</v>
-      </c>
-      <c r="G50" s="73" t="s">
-        <v>31</v>
-      </c>
-      <c r="H50" s="73" t="s">
-        <v>31</v>
-      </c>
-      <c r="I50" s="73" t="s">
-        <v>16</v>
-      </c>
-      <c r="J50" s="109">
-        <v>1</v>
-      </c>
-      <c r="K50" s="9"/>
-    </row>
-    <row r="51" spans="1:11" ht="15.75">
+      <c r="D50" s="65" t="s">
+        <v>30</v>
+      </c>
+      <c r="E50" s="65" t="s">
+        <v>30</v>
+      </c>
+      <c r="F50" s="65" t="s">
+        <v>118</v>
+      </c>
+      <c r="G50" s="65" t="s">
+        <v>30</v>
+      </c>
+      <c r="H50" s="65" t="s">
+        <v>30</v>
+      </c>
+      <c r="I50" s="65" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9">
       <c r="A51" s="1"/>
       <c r="C51" s="2"/>
       <c r="D51" s="2"/>
       <c r="I51" s="7"/>
-      <c r="J51" s="12"/>
-      <c r="K51" s="9"/>
-    </row>
-    <row r="52" spans="1:11" ht="15.75">
+    </row>
+    <row r="52" spans="1:9">
       <c r="A52" s="1"/>
       <c r="C52" s="2"/>
       <c r="D52" s="2"/>
       <c r="I52" s="7"/>
-      <c r="J52" s="12"/>
-      <c r="K52" s="9"/>
-    </row>
-    <row r="53" spans="1:11">
+    </row>
+    <row r="53" spans="1:9">
       <c r="A53" s="1"/>
       <c r="C53" s="2"/>
       <c r="D53" s="2"/>
-      <c r="K53" s="9"/>
-    </row>
-    <row r="54" spans="1:11">
+    </row>
+    <row r="54" spans="1:9">
       <c r="A54" s="1"/>
       <c r="C54" s="2"/>
       <c r="D54" s="2"/>
-      <c r="K54" s="9"/>
-    </row>
-    <row r="55" spans="1:11">
+    </row>
+    <row r="55" spans="1:9">
       <c r="A55" s="1"/>
       <c r="C55" s="2"/>
       <c r="D55" s="2"/>
-      <c r="K55" s="9"/>
-    </row>
-    <row r="56" spans="1:11">
+    </row>
+    <row r="56" spans="1:9">
       <c r="A56" s="1"/>
       <c r="C56" s="2"/>
       <c r="D56" s="2"/>
-      <c r="K56" s="9"/>
-    </row>
-    <row r="57" spans="1:11">
+    </row>
+    <row r="57" spans="1:9">
       <c r="A57" s="1"/>
       <c r="C57" s="2"/>
       <c r="D57" s="2"/>
-      <c r="K57" s="9"/>
-    </row>
-    <row r="58" spans="1:11">
+    </row>
+    <row r="58" spans="1:9">
       <c r="A58" s="1"/>
-      <c r="K58" s="9"/>
-    </row>
-    <row r="59" spans="1:11" ht="15.75" customHeight="1">
+    </row>
+    <row r="59" spans="1:9" ht="15.75" customHeight="1">
       <c r="A59" s="1"/>
-      <c r="K59" s="9"/>
-    </row>
-    <row r="60" spans="1:11">
+    </row>
+    <row r="60" spans="1:9">
       <c r="A60" s="1"/>
-      <c r="K60" s="9"/>
-    </row>
-    <row r="61" spans="1:11">
+    </row>
+    <row r="61" spans="1:9">
       <c r="A61" s="1"/>
-      <c r="K61" s="9"/>
-    </row>
-    <row r="62" spans="1:11">
+    </row>
+    <row r="62" spans="1:9">
       <c r="A62" s="1"/>
-      <c r="K62" s="9"/>
-    </row>
-    <row r="63" spans="1:11">
+    </row>
+    <row r="63" spans="1:9">
       <c r="A63" s="1"/>
-      <c r="K63" s="9"/>
-    </row>
-    <row r="64" spans="1:11">
+    </row>
+    <row r="64" spans="1:9">
       <c r="A64" s="1"/>
-      <c r="K64" s="9"/>
     </row>
     <row r="65" spans="7:7">
       <c r="G65" s="8"/>
@@ -3541,26 +3138,14 @@
     <mergeCell ref="B49:B50"/>
     <mergeCell ref="B3:B17"/>
     <mergeCell ref="B20:B23"/>
-    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A1:I1"/>
     <mergeCell ref="B29:B33"/>
     <mergeCell ref="B34:B42"/>
     <mergeCell ref="B43:B48"/>
     <mergeCell ref="B26:B28"/>
     <mergeCell ref="B18:B19"/>
   </mergeCells>
-  <phoneticPr fontId="9" type="noConversion"/>
-  <conditionalFormatting sqref="J3:J8">
-    <cfRule type="colorScale" priority="13">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
+  <phoneticPr fontId="8" type="noConversion"/>
   <conditionalFormatting sqref="I48">
     <cfRule type="dataBar" priority="54">
       <dataBar>
@@ -3573,42 +3158,6 @@
           <x14:id>{193AFC57-9059-4DAB-9E2A-67F7DD9723ED}</x14:id>
         </ext>
       </extLst>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J50">
-    <cfRule type="colorScale" priority="62">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J9:J28 J34:J49">
-    <cfRule type="colorScale" priority="63">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J3:J49">
-    <cfRule type="colorScale" priority="66">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Deliverables/BOM/eSpark-BOM-v2.0 Boards_PCBWay.xlsx
+++ b/Deliverables/BOM/eSpark-BOM-v2.0 Boards_PCBWay.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="25408"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\Melih-SoundSensor\Deliverables\BOM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Faizan\GitHub\Melih-SoundSensor\Deliverables\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE9EB3AE-8AFA-4F59-A2FA-2EE31933FE47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14016" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="23250" windowHeight="14010"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="239">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="240">
   <si>
     <t>S. No.</t>
   </si>
@@ -742,12 +741,15 @@
   </si>
   <si>
     <t>C2972450</t>
+  </si>
+  <si>
+    <t>Quantity (Per Board)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.0000"/>
   </numFmts>
@@ -895,36 +897,12 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="21">
+  <borders count="25">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1165,6 +1143,84 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -1174,7 +1230,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="83">
+  <cellXfs count="87">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1182,16 +1238,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1206,56 +1262,62 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1263,163 +1325,169 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="9" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="5" borderId="9" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="11" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="5" borderId="11" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="17" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1697,36 +1765,38 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I66"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:J66"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="6.109375" style="2" customWidth="1"/>
-    <col min="2" max="2" width="14.44140625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="47.5546875" style="9" customWidth="1"/>
-    <col min="4" max="4" width="35.109375" style="10" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.5546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="28.44140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.33203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.44140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.140625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="14.42578125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="47.5703125" style="9" customWidth="1"/>
+    <col min="4" max="4" width="35.140625" style="10" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="28.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.42578125" style="2" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="16384" width="9" style="1"/>
+    <col min="10" max="10" width="22.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="16.2" thickBot="1">
-      <c r="A1" s="79" t="s">
+    <row r="1" spans="1:10" ht="16.5" thickBot="1">
+      <c r="A1" s="81" t="s">
         <v>116</v>
       </c>
-      <c r="B1" s="80"/>
-      <c r="C1" s="80"/>
-      <c r="D1" s="80"/>
-      <c r="E1" s="80"/>
-      <c r="F1" s="80"/>
-      <c r="G1" s="80"/>
-      <c r="H1" s="80"/>
-      <c r="I1" s="80"/>
-    </row>
-    <row r="2" spans="1:9" ht="16.2" thickBot="1">
+      <c r="B1" s="82"/>
+      <c r="C1" s="82"/>
+      <c r="D1" s="82"/>
+      <c r="E1" s="82"/>
+      <c r="F1" s="82"/>
+      <c r="G1" s="82"/>
+      <c r="H1" s="82"/>
+      <c r="I1" s="82"/>
+      <c r="J1" s="82"/>
+    </row>
+    <row r="2" spans="1:10" ht="16.5" thickBot="1">
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
@@ -1754,8 +1824,11 @@
       <c r="I2" s="49" t="s">
         <v>199</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" ht="15" thickBot="1">
+      <c r="J2" s="3" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="15.75" thickBot="1">
       <c r="A3" s="6">
         <v>1</v>
       </c>
@@ -1783,8 +1856,11 @@
       <c r="I3" s="13">
         <v>100</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" ht="15" thickBot="1">
+      <c r="J3" s="83">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="15.75" thickBot="1">
       <c r="A4" s="6">
         <v>2</v>
       </c>
@@ -1810,8 +1886,11 @@
       <c r="I4" s="17">
         <v>40</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" ht="42" thickBot="1">
+      <c r="J4" s="84">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="39" thickBot="1">
       <c r="A5" s="6">
         <v>3</v>
       </c>
@@ -1837,8 +1916,11 @@
       <c r="I5" s="17">
         <v>400</v>
       </c>
-    </row>
-    <row r="6" spans="1:9" ht="15" thickBot="1">
+      <c r="J5" s="84">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="15.75" thickBot="1">
       <c r="A6" s="6">
         <v>4</v>
       </c>
@@ -1864,8 +1946,11 @@
       <c r="I6" s="17">
         <v>200</v>
       </c>
-    </row>
-    <row r="7" spans="1:9" ht="15" thickBot="1">
+      <c r="J6" s="84">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="15.75" thickBot="1">
       <c r="A7" s="6">
         <v>5</v>
       </c>
@@ -1891,8 +1976,11 @@
       <c r="I7" s="17">
         <v>100</v>
       </c>
-    </row>
-    <row r="8" spans="1:9" ht="55.8" thickBot="1">
+      <c r="J7" s="84">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="51.75" thickBot="1">
       <c r="A8" s="6">
         <v>6</v>
       </c>
@@ -1918,8 +2006,11 @@
       <c r="I8" s="17">
         <v>600</v>
       </c>
-    </row>
-    <row r="9" spans="1:9" ht="15" thickBot="1">
+      <c r="J8" s="84">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="15.75" thickBot="1">
       <c r="A9" s="6">
         <v>7</v>
       </c>
@@ -1945,8 +2036,11 @@
       <c r="I9" s="18">
         <v>30</v>
       </c>
-    </row>
-    <row r="10" spans="1:9" ht="15" thickBot="1">
+      <c r="J9" s="84">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="15.75" thickBot="1">
       <c r="A10" s="6">
         <v>8</v>
       </c>
@@ -1972,8 +2066,11 @@
       <c r="I10" s="18">
         <v>200</v>
       </c>
-    </row>
-    <row r="11" spans="1:9" ht="28.2" thickBot="1">
+      <c r="J10" s="84">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="26.25" thickBot="1">
       <c r="A11" s="6">
         <v>9</v>
       </c>
@@ -1999,8 +2096,11 @@
       <c r="I11" s="18">
         <v>350</v>
       </c>
-    </row>
-    <row r="12" spans="1:9" ht="15" thickBot="1">
+      <c r="J11" s="84">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="15.75" thickBot="1">
       <c r="A12" s="6">
         <v>10</v>
       </c>
@@ -2026,8 +2126,11 @@
       <c r="I12" s="18">
         <v>50</v>
       </c>
-    </row>
-    <row r="13" spans="1:9" ht="15" thickBot="1">
+      <c r="J12" s="84">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="15.75" thickBot="1">
       <c r="A13" s="6">
         <v>11</v>
       </c>
@@ -2053,8 +2156,11 @@
       <c r="I13" s="18">
         <v>100</v>
       </c>
-    </row>
-    <row r="14" spans="1:9" ht="15" thickBot="1">
+      <c r="J13" s="84">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="15.75" thickBot="1">
       <c r="A14" s="6">
         <v>12</v>
       </c>
@@ -2080,8 +2186,11 @@
       <c r="I14" s="18">
         <v>100</v>
       </c>
-    </row>
-    <row r="15" spans="1:9" ht="15" thickBot="1">
+      <c r="J14" s="84">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="15.75" thickBot="1">
       <c r="A15" s="6">
         <v>13</v>
       </c>
@@ -2107,8 +2216,11 @@
       <c r="I15" s="18">
         <v>50</v>
       </c>
-    </row>
-    <row r="16" spans="1:9" ht="15" thickBot="1">
+      <c r="J15" s="84">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="15.75" thickBot="1">
       <c r="A16" s="6">
         <v>14</v>
       </c>
@@ -2134,8 +2246,11 @@
       <c r="I16" s="18">
         <v>50</v>
       </c>
-    </row>
-    <row r="17" spans="1:9" ht="15" thickBot="1">
+      <c r="J16" s="84">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="15.75" thickBot="1">
       <c r="A17" s="6">
         <v>15</v>
       </c>
@@ -2161,12 +2276,15 @@
       <c r="I17" s="24">
         <v>50</v>
       </c>
-    </row>
-    <row r="18" spans="1:9" ht="28.2" thickBot="1">
+      <c r="J17" s="85">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="26.25" thickBot="1">
       <c r="A18" s="6">
         <v>16</v>
       </c>
-      <c r="B18" s="81" t="s">
+      <c r="B18" s="79" t="s">
         <v>148</v>
       </c>
       <c r="C18" s="50" t="s">
@@ -2190,12 +2308,15 @@
       <c r="I18" s="11">
         <v>30</v>
       </c>
-    </row>
-    <row r="19" spans="1:9" ht="15" thickBot="1">
+      <c r="J18" s="86">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="15.75" thickBot="1">
       <c r="A19" s="6">
         <v>17</v>
       </c>
-      <c r="B19" s="82"/>
+      <c r="B19" s="80"/>
       <c r="C19" s="51" t="s">
         <v>178</v>
       </c>
@@ -2217,8 +2338,11 @@
       <c r="I19" s="24">
         <v>50</v>
       </c>
-    </row>
-    <row r="20" spans="1:9" ht="15" thickBot="1">
+      <c r="J19" s="85">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="15.75" thickBot="1">
       <c r="A20" s="6">
         <v>18</v>
       </c>
@@ -2246,8 +2370,11 @@
       <c r="I20" s="11">
         <v>50</v>
       </c>
-    </row>
-    <row r="21" spans="1:9" ht="15" thickBot="1">
+      <c r="J20" s="86">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="15.75" thickBot="1">
       <c r="A21" s="6">
         <v>19</v>
       </c>
@@ -2273,8 +2400,11 @@
       <c r="I21" s="18">
         <v>45</v>
       </c>
-    </row>
-    <row r="22" spans="1:9" ht="15" thickBot="1">
+      <c r="J21" s="84">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="15.75" thickBot="1">
       <c r="A22" s="6">
         <v>20</v>
       </c>
@@ -2300,8 +2430,11 @@
       <c r="I22" s="18">
         <v>50</v>
       </c>
-    </row>
-    <row r="23" spans="1:9" ht="15" thickBot="1">
+      <c r="J22" s="84">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" ht="15.75" thickBot="1">
       <c r="A23" s="6">
         <v>21</v>
       </c>
@@ -2327,8 +2460,11 @@
       <c r="I23" s="24">
         <v>30</v>
       </c>
-    </row>
-    <row r="24" spans="1:9" ht="28.2" thickBot="1">
+      <c r="J23" s="85">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" ht="26.25" thickBot="1">
       <c r="A24" s="6">
         <v>22</v>
       </c>
@@ -2356,8 +2492,11 @@
       <c r="I24" s="60">
         <v>162</v>
       </c>
-    </row>
-    <row r="25" spans="1:9" ht="28.2" thickBot="1">
+      <c r="J24" s="86">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" ht="26.25" thickBot="1">
       <c r="A25" s="6">
         <v>23</v>
       </c>
@@ -2385,8 +2524,11 @@
       <c r="I25" s="32">
         <v>30</v>
       </c>
-    </row>
-    <row r="26" spans="1:9" ht="28.2" thickBot="1">
+      <c r="J25" s="85">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" ht="26.25" thickBot="1">
       <c r="A26" s="6">
         <v>24</v>
       </c>
@@ -2414,8 +2556,11 @@
       <c r="I26" s="23">
         <v>22</v>
       </c>
-    </row>
-    <row r="27" spans="1:9" ht="28.2" thickBot="1">
+      <c r="J26" s="86">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" ht="26.25" thickBot="1">
       <c r="A27" s="6">
         <v>25</v>
       </c>
@@ -2441,8 +2586,11 @@
       <c r="I27" s="17">
         <v>45</v>
       </c>
-    </row>
-    <row r="28" spans="1:9" ht="28.2" thickBot="1">
+      <c r="J27" s="84">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" ht="26.25" thickBot="1">
       <c r="A28" s="6">
         <v>26</v>
       </c>
@@ -2468,8 +2616,11 @@
       <c r="I28" s="26">
         <v>25</v>
       </c>
-    </row>
-    <row r="29" spans="1:9" ht="15" thickBot="1">
+      <c r="J28" s="85">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" ht="15.75" thickBot="1">
       <c r="A29" s="6">
         <v>27</v>
       </c>
@@ -2497,8 +2648,11 @@
       <c r="I29" s="53">
         <v>100</v>
       </c>
-    </row>
-    <row r="30" spans="1:9" ht="15" thickBot="1">
+      <c r="J29" s="86">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" ht="15.75" thickBot="1">
       <c r="A30" s="6">
         <v>28</v>
       </c>
@@ -2524,8 +2678,11 @@
       <c r="I30" s="37">
         <v>100</v>
       </c>
-    </row>
-    <row r="31" spans="1:9" ht="15" thickBot="1">
+      <c r="J30" s="84">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" ht="15.75" thickBot="1">
       <c r="A31" s="6">
         <v>29</v>
       </c>
@@ -2551,8 +2708,11 @@
       <c r="I31" s="37">
         <v>100</v>
       </c>
-    </row>
-    <row r="32" spans="1:9" ht="15" thickBot="1">
+      <c r="J31" s="84">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" ht="15.75" thickBot="1">
       <c r="A32" s="6">
         <v>30</v>
       </c>
@@ -2578,8 +2738,11 @@
       <c r="I32" s="37">
         <v>100</v>
       </c>
-    </row>
-    <row r="33" spans="1:9" ht="15" thickBot="1">
+      <c r="J32" s="84">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" ht="15.75" thickBot="1">
       <c r="A33" s="6">
         <v>31</v>
       </c>
@@ -2605,8 +2768,11 @@
       <c r="I33" s="55">
         <v>100</v>
       </c>
-    </row>
-    <row r="34" spans="1:9" ht="15" thickBot="1">
+      <c r="J33" s="85">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" ht="15.75" thickBot="1">
       <c r="A34" s="6">
         <v>32</v>
       </c>
@@ -2634,8 +2800,11 @@
       <c r="I34" s="13">
         <v>42</v>
       </c>
-    </row>
-    <row r="35" spans="1:9" ht="28.2" thickBot="1">
+      <c r="J34" s="86">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" ht="26.25" thickBot="1">
       <c r="A35" s="6">
         <v>33</v>
       </c>
@@ -2661,8 +2830,11 @@
       <c r="I35" s="16">
         <v>21</v>
       </c>
-    </row>
-    <row r="36" spans="1:9" ht="15" thickBot="1">
+      <c r="J35" s="84">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" ht="15.75" thickBot="1">
       <c r="A36" s="6">
         <v>34</v>
       </c>
@@ -2688,8 +2860,11 @@
       <c r="I36" s="18">
         <v>21</v>
       </c>
-    </row>
-    <row r="37" spans="1:9" ht="15" thickBot="1">
+      <c r="J36" s="84">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" ht="15.75" thickBot="1">
       <c r="A37" s="6">
         <v>35</v>
       </c>
@@ -2715,8 +2890,11 @@
       <c r="I37" s="18">
         <v>41</v>
       </c>
-    </row>
-    <row r="38" spans="1:9" ht="15" thickBot="1">
+      <c r="J37" s="84">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" ht="15.75" thickBot="1">
       <c r="A38" s="6">
         <v>36</v>
       </c>
@@ -2742,8 +2920,11 @@
       <c r="I38" s="18">
         <v>21</v>
       </c>
-    </row>
-    <row r="39" spans="1:9" ht="15" thickBot="1">
+      <c r="J38" s="84">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" ht="15.75" thickBot="1">
       <c r="A39" s="6">
         <v>37</v>
       </c>
@@ -2769,8 +2950,11 @@
       <c r="I39" s="18">
         <v>21</v>
       </c>
-    </row>
-    <row r="40" spans="1:9" ht="15" thickBot="1">
+      <c r="J39" s="84">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" ht="15.75" thickBot="1">
       <c r="A40" s="6">
         <v>38</v>
       </c>
@@ -2796,8 +2980,11 @@
       <c r="I40" s="18">
         <v>22</v>
       </c>
-    </row>
-    <row r="41" spans="1:9" ht="15" thickBot="1">
+      <c r="J40" s="84">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" ht="15.75" thickBot="1">
       <c r="A41" s="6">
         <v>39</v>
       </c>
@@ -2823,8 +3010,11 @@
       <c r="I41" s="20">
         <v>30</v>
       </c>
-    </row>
-    <row r="42" spans="1:9" ht="28.2" thickBot="1">
+      <c r="J41" s="84">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" ht="26.25" thickBot="1">
       <c r="A42" s="6">
         <v>40</v>
       </c>
@@ -2850,8 +3040,11 @@
       <c r="I42" s="24">
         <v>30</v>
       </c>
-    </row>
-    <row r="43" spans="1:9" ht="15" thickBot="1">
+      <c r="J42" s="85">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" ht="15.75" thickBot="1">
       <c r="A43" s="6">
         <v>41</v>
       </c>
@@ -2879,8 +3072,11 @@
       <c r="I43" s="27">
         <v>50</v>
       </c>
-    </row>
-    <row r="44" spans="1:9" ht="28.2" thickBot="1">
+      <c r="J43" s="86">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" ht="26.25" thickBot="1">
       <c r="A44" s="6">
         <v>42</v>
       </c>
@@ -2906,8 +3102,11 @@
       <c r="I44" s="17">
         <v>30</v>
       </c>
-    </row>
-    <row r="45" spans="1:9" ht="15" thickBot="1">
+      <c r="J44" s="84">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" ht="15.75" thickBot="1">
       <c r="A45" s="6">
         <v>43</v>
       </c>
@@ -2933,8 +3132,11 @@
       <c r="I45" s="17">
         <v>50</v>
       </c>
-    </row>
-    <row r="46" spans="1:9" ht="15" thickBot="1">
+      <c r="J45" s="84">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" ht="15.75" thickBot="1">
       <c r="A46" s="6">
         <v>44</v>
       </c>
@@ -2960,8 +3162,11 @@
       <c r="I46" s="17">
         <v>25</v>
       </c>
-    </row>
-    <row r="47" spans="1:9" ht="15" thickBot="1">
+      <c r="J46" s="84">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" ht="15.75" thickBot="1">
       <c r="A47" s="6">
         <v>45</v>
       </c>
@@ -2987,8 +3192,11 @@
       <c r="I47" s="32">
         <v>40</v>
       </c>
-    </row>
-    <row r="48" spans="1:9" ht="111" thickBot="1">
+      <c r="J47" s="84">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" ht="102.75" thickBot="1">
       <c r="A48" s="6">
         <v>46</v>
       </c>
@@ -3012,8 +3220,11 @@
       <c r="I48" s="44" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="49" spans="1:9" ht="28.2" thickBot="1">
+      <c r="J48" s="85">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" ht="26.25" thickBot="1">
       <c r="A49" s="6">
         <v>47</v>
       </c>
@@ -3041,8 +3252,11 @@
       <c r="I49" s="63" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="50" spans="1:9" ht="15" thickBot="1">
+      <c r="J49" s="86">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" ht="15.75" thickBot="1">
       <c r="A50" s="72">
         <v>48</v>
       </c>
@@ -3068,63 +3282,66 @@
       <c r="I50" s="65" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="51" spans="1:9">
+      <c r="J50" s="85">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10">
       <c r="A51" s="1"/>
       <c r="C51" s="2"/>
       <c r="D51" s="2"/>
       <c r="I51" s="7"/>
     </row>
-    <row r="52" spans="1:9">
+    <row r="52" spans="1:10">
       <c r="A52" s="1"/>
       <c r="C52" s="2"/>
       <c r="D52" s="2"/>
       <c r="I52" s="7"/>
     </row>
-    <row r="53" spans="1:9">
+    <row r="53" spans="1:10">
       <c r="A53" s="1"/>
       <c r="C53" s="2"/>
       <c r="D53" s="2"/>
     </row>
-    <row r="54" spans="1:9">
+    <row r="54" spans="1:10">
       <c r="A54" s="1"/>
       <c r="C54" s="2"/>
       <c r="D54" s="2"/>
     </row>
-    <row r="55" spans="1:9">
+    <row r="55" spans="1:10">
       <c r="A55" s="1"/>
       <c r="C55" s="2"/>
       <c r="D55" s="2"/>
     </row>
-    <row r="56" spans="1:9">
+    <row r="56" spans="1:10">
       <c r="A56" s="1"/>
       <c r="C56" s="2"/>
       <c r="D56" s="2"/>
     </row>
-    <row r="57" spans="1:9">
+    <row r="57" spans="1:10">
       <c r="A57" s="1"/>
       <c r="C57" s="2"/>
       <c r="D57" s="2"/>
     </row>
-    <row r="58" spans="1:9">
+    <row r="58" spans="1:10">
       <c r="A58" s="1"/>
     </row>
-    <row r="59" spans="1:9" ht="15.75" customHeight="1">
+    <row r="59" spans="1:10" ht="15.75" customHeight="1">
       <c r="A59" s="1"/>
     </row>
-    <row r="60" spans="1:9">
+    <row r="60" spans="1:10">
       <c r="A60" s="1"/>
     </row>
-    <row r="61" spans="1:9">
+    <row r="61" spans="1:10">
       <c r="A61" s="1"/>
     </row>
-    <row r="62" spans="1:9">
+    <row r="62" spans="1:10">
       <c r="A62" s="1"/>
     </row>
-    <row r="63" spans="1:9">
+    <row r="63" spans="1:10">
       <c r="A63" s="1"/>
     </row>
-    <row r="64" spans="1:9">
+    <row r="64" spans="1:10">
       <c r="A64" s="1"/>
     </row>
     <row r="65" spans="7:7">
@@ -3138,16 +3355,16 @@
     <mergeCell ref="B49:B50"/>
     <mergeCell ref="B3:B17"/>
     <mergeCell ref="B20:B23"/>
-    <mergeCell ref="A1:I1"/>
     <mergeCell ref="B29:B33"/>
     <mergeCell ref="B34:B42"/>
     <mergeCell ref="B43:B48"/>
     <mergeCell ref="B26:B28"/>
     <mergeCell ref="B18:B19"/>
+    <mergeCell ref="A1:J1"/>
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <conditionalFormatting sqref="I48">
-    <cfRule type="dataBar" priority="54">
+    <cfRule type="dataBar" priority="59">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>

--- a/Deliverables/BOM/eSpark-BOM-v2.0 Boards_PCBWay.xlsx
+++ b/Deliverables/BOM/eSpark-BOM-v2.0 Boards_PCBWay.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="25225"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Faizan\GitHub\Melih-SoundSensor\Deliverables\BOM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\Melih-SoundSensor\Deliverables\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0065F40-298B-4822-BB41-3C0E080A3BC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="-105" windowWidth="23250" windowHeight="14010"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -19,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="240">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="245">
   <si>
     <t>S. No.</t>
   </si>
@@ -744,12 +745,27 @@
   </si>
   <si>
     <t>Quantity (Per Board)</t>
+  </si>
+  <si>
+    <t>RES SMD 5.1K OHM 5% 1/10W 0603</t>
+  </si>
+  <si>
+    <t>R11, R12</t>
+  </si>
+  <si>
+    <t>RC0603JR-075K1L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">YAGEO </t>
+  </si>
+  <si>
+    <t>5.1K</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.0000"/>
   </numFmts>
@@ -897,7 +913,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="25">
+  <borders count="26">
     <border>
       <left/>
       <right/>
@@ -1144,11 +1160,71 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="medium">
-        <color auto="1"/>
+        <color indexed="64"/>
       </left>
       <right/>
-      <top/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
       <bottom style="medium">
         <color auto="1"/>
       </bottom>
@@ -1157,66 +1233,23 @@
     <border>
       <left/>
       <right/>
-      <top/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
       <bottom style="medium">
         <color auto="1"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
+      <left/>
       <right style="medium">
         <color indexed="64"/>
       </right>
       <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
         <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
       </top>
       <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
         <color auto="1"/>
       </bottom>
       <diagonal/>
@@ -1230,7 +1263,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="87">
+  <cellXfs count="89">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1397,12 +1430,6 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1439,55 +1466,67 @@
     <xf numFmtId="0" fontId="11" fillId="4" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1765,8 +1804,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J66"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:J67"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="2" customWidth="1"/>
@@ -1783,18 +1822,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="16.5" thickBot="1">
-      <c r="A1" s="81" t="s">
+      <c r="A1" s="84" t="s">
         <v>116</v>
       </c>
-      <c r="B1" s="82"/>
-      <c r="C1" s="82"/>
-      <c r="D1" s="82"/>
-      <c r="E1" s="82"/>
-      <c r="F1" s="82"/>
-      <c r="G1" s="82"/>
-      <c r="H1" s="82"/>
-      <c r="I1" s="82"/>
-      <c r="J1" s="82"/>
+      <c r="B1" s="85"/>
+      <c r="C1" s="85"/>
+      <c r="D1" s="85"/>
+      <c r="E1" s="85"/>
+      <c r="F1" s="85"/>
+      <c r="G1" s="85"/>
+      <c r="H1" s="85"/>
+      <c r="I1" s="85"/>
+      <c r="J1" s="86"/>
     </row>
     <row r="2" spans="1:10" ht="16.5" thickBot="1">
       <c r="A2" s="3" t="s">
@@ -1832,7 +1871,7 @@
       <c r="A3" s="6">
         <v>1</v>
       </c>
-      <c r="B3" s="75" t="s">
+      <c r="B3" s="77" t="s">
         <v>8</v>
       </c>
       <c r="C3" s="28" t="s">
@@ -1856,7 +1895,7 @@
       <c r="I3" s="13">
         <v>100</v>
       </c>
-      <c r="J3" s="83">
+      <c r="J3" s="71">
         <v>4</v>
       </c>
     </row>
@@ -1864,7 +1903,7 @@
       <c r="A4" s="6">
         <v>2</v>
       </c>
-      <c r="B4" s="76"/>
+      <c r="B4" s="78"/>
       <c r="C4" s="30" t="s">
         <v>14</v>
       </c>
@@ -1886,7 +1925,7 @@
       <c r="I4" s="17">
         <v>40</v>
       </c>
-      <c r="J4" s="84">
+      <c r="J4" s="72">
         <v>1</v>
       </c>
     </row>
@@ -1894,7 +1933,7 @@
       <c r="A5" s="6">
         <v>3</v>
       </c>
-      <c r="B5" s="76"/>
+      <c r="B5" s="78"/>
       <c r="C5" s="30" t="s">
         <v>38</v>
       </c>
@@ -1916,7 +1955,7 @@
       <c r="I5" s="17">
         <v>400</v>
       </c>
-      <c r="J5" s="84">
+      <c r="J5" s="72">
         <v>19</v>
       </c>
     </row>
@@ -1924,7 +1963,7 @@
       <c r="A6" s="6">
         <v>4</v>
       </c>
-      <c r="B6" s="76"/>
+      <c r="B6" s="78"/>
       <c r="C6" s="30" t="s">
         <v>40</v>
       </c>
@@ -1946,7 +1985,7 @@
       <c r="I6" s="17">
         <v>200</v>
       </c>
-      <c r="J6" s="84">
+      <c r="J6" s="72">
         <v>8</v>
       </c>
     </row>
@@ -1954,7 +1993,7 @@
       <c r="A7" s="6">
         <v>5</v>
       </c>
-      <c r="B7" s="76"/>
+      <c r="B7" s="78"/>
       <c r="C7" s="30" t="s">
         <v>120</v>
       </c>
@@ -1976,7 +2015,7 @@
       <c r="I7" s="17">
         <v>100</v>
       </c>
-      <c r="J7" s="84">
+      <c r="J7" s="72">
         <v>1</v>
       </c>
     </row>
@@ -1984,7 +2023,7 @@
       <c r="A8" s="6">
         <v>6</v>
       </c>
-      <c r="B8" s="76"/>
+      <c r="B8" s="78"/>
       <c r="C8" s="30" t="s">
         <v>10</v>
       </c>
@@ -2006,7 +2045,7 @@
       <c r="I8" s="17">
         <v>600</v>
       </c>
-      <c r="J8" s="84">
+      <c r="J8" s="72">
         <v>29</v>
       </c>
     </row>
@@ -2014,7 +2053,7 @@
       <c r="A9" s="6">
         <v>7</v>
       </c>
-      <c r="B9" s="76"/>
+      <c r="B9" s="78"/>
       <c r="C9" s="30" t="s">
         <v>44</v>
       </c>
@@ -2036,7 +2075,7 @@
       <c r="I9" s="18">
         <v>30</v>
       </c>
-      <c r="J9" s="84">
+      <c r="J9" s="72">
         <v>1</v>
       </c>
     </row>
@@ -2044,7 +2083,7 @@
       <c r="A10" s="6">
         <v>8</v>
       </c>
-      <c r="B10" s="76"/>
+      <c r="B10" s="78"/>
       <c r="C10" s="30" t="s">
         <v>47</v>
       </c>
@@ -2066,7 +2105,7 @@
       <c r="I10" s="18">
         <v>200</v>
       </c>
-      <c r="J10" s="84">
+      <c r="J10" s="72">
         <v>6</v>
       </c>
     </row>
@@ -2074,7 +2113,7 @@
       <c r="A11" s="6">
         <v>9</v>
       </c>
-      <c r="B11" s="76"/>
+      <c r="B11" s="78"/>
       <c r="C11" s="30" t="s">
         <v>50</v>
       </c>
@@ -2096,7 +2135,7 @@
       <c r="I11" s="18">
         <v>350</v>
       </c>
-      <c r="J11" s="84">
+      <c r="J11" s="72">
         <v>16</v>
       </c>
     </row>
@@ -2104,7 +2143,7 @@
       <c r="A12" s="6">
         <v>10</v>
       </c>
-      <c r="B12" s="76"/>
+      <c r="B12" s="78"/>
       <c r="C12" s="30" t="s">
         <v>124</v>
       </c>
@@ -2126,7 +2165,7 @@
       <c r="I12" s="18">
         <v>50</v>
       </c>
-      <c r="J12" s="84">
+      <c r="J12" s="72">
         <v>1</v>
       </c>
     </row>
@@ -2134,7 +2173,7 @@
       <c r="A13" s="6">
         <v>11</v>
       </c>
-      <c r="B13" s="76"/>
+      <c r="B13" s="78"/>
       <c r="C13" s="30" t="s">
         <v>127</v>
       </c>
@@ -2156,7 +2195,7 @@
       <c r="I13" s="18">
         <v>100</v>
       </c>
-      <c r="J13" s="84">
+      <c r="J13" s="72">
         <v>1</v>
       </c>
     </row>
@@ -2164,7 +2203,7 @@
       <c r="A14" s="6">
         <v>12</v>
       </c>
-      <c r="B14" s="76"/>
+      <c r="B14" s="78"/>
       <c r="C14" s="30" t="s">
         <v>172</v>
       </c>
@@ -2186,7 +2225,7 @@
       <c r="I14" s="18">
         <v>100</v>
       </c>
-      <c r="J14" s="84">
+      <c r="J14" s="72">
         <v>1</v>
       </c>
     </row>
@@ -2194,7 +2233,7 @@
       <c r="A15" s="6">
         <v>13</v>
       </c>
-      <c r="B15" s="76"/>
+      <c r="B15" s="78"/>
       <c r="C15" s="30" t="s">
         <v>175</v>
       </c>
@@ -2216,7 +2255,7 @@
       <c r="I15" s="18">
         <v>50</v>
       </c>
-      <c r="J15" s="84">
+      <c r="J15" s="72">
         <v>2</v>
       </c>
     </row>
@@ -2224,7 +2263,7 @@
       <c r="A16" s="6">
         <v>14</v>
       </c>
-      <c r="B16" s="76"/>
+      <c r="B16" s="78"/>
       <c r="C16" s="30" t="s">
         <v>202</v>
       </c>
@@ -2246,7 +2285,7 @@
       <c r="I16" s="18">
         <v>50</v>
       </c>
-      <c r="J16" s="84">
+      <c r="J16" s="72">
         <v>1</v>
       </c>
     </row>
@@ -2254,7 +2293,7 @@
       <c r="A17" s="6">
         <v>15</v>
       </c>
-      <c r="B17" s="77"/>
+      <c r="B17" s="79"/>
       <c r="C17" s="39" t="s">
         <v>205</v>
       </c>
@@ -2276,7 +2315,7 @@
       <c r="I17" s="24">
         <v>50</v>
       </c>
-      <c r="J17" s="85">
+      <c r="J17" s="73">
         <v>1</v>
       </c>
     </row>
@@ -2284,7 +2323,7 @@
       <c r="A18" s="6">
         <v>16</v>
       </c>
-      <c r="B18" s="79" t="s">
+      <c r="B18" s="81" t="s">
         <v>148</v>
       </c>
       <c r="C18" s="50" t="s">
@@ -2308,7 +2347,7 @@
       <c r="I18" s="11">
         <v>30</v>
       </c>
-      <c r="J18" s="86">
+      <c r="J18" s="74">
         <v>1</v>
       </c>
     </row>
@@ -2316,7 +2355,7 @@
       <c r="A19" s="6">
         <v>17</v>
       </c>
-      <c r="B19" s="80"/>
+      <c r="B19" s="82"/>
       <c r="C19" s="51" t="s">
         <v>178</v>
       </c>
@@ -2338,7 +2377,7 @@
       <c r="I19" s="24">
         <v>50</v>
       </c>
-      <c r="J19" s="85">
+      <c r="J19" s="73">
         <v>2</v>
       </c>
     </row>
@@ -2346,7 +2385,7 @@
       <c r="A20" s="6">
         <v>18</v>
       </c>
-      <c r="B20" s="78" t="s">
+      <c r="B20" s="80" t="s">
         <v>153</v>
       </c>
       <c r="C20" s="28" t="s">
@@ -2370,7 +2409,7 @@
       <c r="I20" s="11">
         <v>50</v>
       </c>
-      <c r="J20" s="86">
+      <c r="J20" s="74">
         <v>1</v>
       </c>
     </row>
@@ -2378,7 +2417,7 @@
       <c r="A21" s="6">
         <v>19</v>
       </c>
-      <c r="B21" s="73"/>
+      <c r="B21" s="75"/>
       <c r="C21" s="30" t="s">
         <v>185</v>
       </c>
@@ -2400,7 +2439,7 @@
       <c r="I21" s="18">
         <v>45</v>
       </c>
-      <c r="J21" s="84">
+      <c r="J21" s="72">
         <v>2</v>
       </c>
     </row>
@@ -2408,7 +2447,7 @@
       <c r="A22" s="6">
         <v>20</v>
       </c>
-      <c r="B22" s="73"/>
+      <c r="B22" s="75"/>
       <c r="C22" s="30" t="s">
         <v>188</v>
       </c>
@@ -2430,7 +2469,7 @@
       <c r="I22" s="18">
         <v>50</v>
       </c>
-      <c r="J22" s="84">
+      <c r="J22" s="72">
         <v>2</v>
       </c>
     </row>
@@ -2438,7 +2477,7 @@
       <c r="A23" s="6">
         <v>21</v>
       </c>
-      <c r="B23" s="74"/>
+      <c r="B23" s="76"/>
       <c r="C23" s="39" t="s">
         <v>212</v>
       </c>
@@ -2460,7 +2499,7 @@
       <c r="I23" s="24">
         <v>30</v>
       </c>
-      <c r="J23" s="85">
+      <c r="J23" s="73">
         <v>1</v>
       </c>
     </row>
@@ -2468,31 +2507,31 @@
       <c r="A24" s="6">
         <v>22</v>
       </c>
-      <c r="B24" s="57" t="s">
+      <c r="B24" s="70" t="s">
         <v>61</v>
       </c>
-      <c r="C24" s="59" t="s">
+      <c r="C24" s="57" t="s">
         <v>58</v>
       </c>
-      <c r="D24" s="67" t="s">
+      <c r="D24" s="65" t="s">
         <v>59</v>
       </c>
-      <c r="E24" s="60" t="s">
+      <c r="E24" s="58" t="s">
         <v>21</v>
       </c>
-      <c r="F24" s="60" t="s">
+      <c r="F24" s="58" t="s">
         <v>60</v>
       </c>
-      <c r="G24" s="61" t="s">
+      <c r="G24" s="59" t="s">
         <v>114</v>
       </c>
-      <c r="H24" s="60" t="s">
+      <c r="H24" s="58" t="s">
         <v>15</v>
       </c>
-      <c r="I24" s="60">
+      <c r="I24" s="58">
         <v>162</v>
       </c>
-      <c r="J24" s="86">
+      <c r="J24" s="74">
         <v>8</v>
       </c>
     </row>
@@ -2500,13 +2539,13 @@
       <c r="A25" s="6">
         <v>23</v>
       </c>
-      <c r="B25" s="56" t="s">
+      <c r="B25" s="69" t="s">
         <v>19</v>
       </c>
       <c r="C25" s="38" t="s">
         <v>62</v>
       </c>
-      <c r="D25" s="68" t="s">
+      <c r="D25" s="66" t="s">
         <v>20</v>
       </c>
       <c r="E25" s="32" t="s">
@@ -2524,7 +2563,7 @@
       <c r="I25" s="32">
         <v>30</v>
       </c>
-      <c r="J25" s="85">
+      <c r="J25" s="73">
         <v>1</v>
       </c>
     </row>
@@ -2532,7 +2571,7 @@
       <c r="A26" s="6">
         <v>24</v>
       </c>
-      <c r="B26" s="75" t="s">
+      <c r="B26" s="77" t="s">
         <v>24</v>
       </c>
       <c r="C26" s="33" t="s">
@@ -2556,7 +2595,7 @@
       <c r="I26" s="23">
         <v>22</v>
       </c>
-      <c r="J26" s="86">
+      <c r="J26" s="74">
         <v>1</v>
       </c>
     </row>
@@ -2564,7 +2603,7 @@
       <c r="A27" s="6">
         <v>25</v>
       </c>
-      <c r="B27" s="76"/>
+      <c r="B27" s="78"/>
       <c r="C27" s="35" t="s">
         <v>66</v>
       </c>
@@ -2586,7 +2625,7 @@
       <c r="I27" s="17">
         <v>45</v>
       </c>
-      <c r="J27" s="84">
+      <c r="J27" s="72">
         <v>2</v>
       </c>
     </row>
@@ -2594,7 +2633,7 @@
       <c r="A28" s="6">
         <v>26</v>
       </c>
-      <c r="B28" s="77"/>
+      <c r="B28" s="79"/>
       <c r="C28" s="34" t="s">
         <v>129</v>
       </c>
@@ -2616,7 +2655,7 @@
       <c r="I28" s="26">
         <v>25</v>
       </c>
-      <c r="J28" s="85">
+      <c r="J28" s="73">
         <v>1</v>
       </c>
     </row>
@@ -2624,7 +2663,7 @@
       <c r="A29" s="6">
         <v>27</v>
       </c>
-      <c r="B29" s="75" t="s">
+      <c r="B29" s="77" t="s">
         <v>16</v>
       </c>
       <c r="C29" s="33" t="s">
@@ -2648,7 +2687,7 @@
       <c r="I29" s="53">
         <v>100</v>
       </c>
-      <c r="J29" s="86">
+      <c r="J29" s="71">
         <v>3</v>
       </c>
     </row>
@@ -2656,7 +2695,7 @@
       <c r="A30" s="6">
         <v>28</v>
       </c>
-      <c r="B30" s="76"/>
+      <c r="B30" s="78"/>
       <c r="C30" s="35" t="s">
         <v>217</v>
       </c>
@@ -2678,7 +2717,7 @@
       <c r="I30" s="37">
         <v>100</v>
       </c>
-      <c r="J30" s="84">
+      <c r="J30" s="72">
         <v>1</v>
       </c>
     </row>
@@ -2686,7 +2725,7 @@
       <c r="A31" s="6">
         <v>29</v>
       </c>
-      <c r="B31" s="76"/>
+      <c r="B31" s="78"/>
       <c r="C31" s="35" t="s">
         <v>134</v>
       </c>
@@ -2708,7 +2747,7 @@
       <c r="I31" s="37">
         <v>100</v>
       </c>
-      <c r="J31" s="84">
+      <c r="J31" s="72">
         <v>1</v>
       </c>
     </row>
@@ -2716,7 +2755,7 @@
       <c r="A32" s="6">
         <v>30</v>
       </c>
-      <c r="B32" s="76"/>
+      <c r="B32" s="78"/>
       <c r="C32" s="35" t="s">
         <v>193</v>
       </c>
@@ -2738,7 +2777,7 @@
       <c r="I32" s="37">
         <v>100</v>
       </c>
-      <c r="J32" s="84">
+      <c r="J32" s="72">
         <v>4</v>
       </c>
     </row>
@@ -2746,29 +2785,29 @@
       <c r="A33" s="6">
         <v>31</v>
       </c>
-      <c r="B33" s="77"/>
-      <c r="C33" s="34" t="s">
+      <c r="B33" s="78"/>
+      <c r="C33" s="35" t="s">
         <v>70</v>
       </c>
-      <c r="D33" s="54" t="s">
+      <c r="D33" s="46" t="s">
         <v>227</v>
       </c>
-      <c r="E33" s="26" t="s">
+      <c r="E33" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="F33" s="26" t="s">
+      <c r="F33" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="G33" s="25" t="s">
+      <c r="G33" s="15" t="s">
         <v>107</v>
       </c>
-      <c r="H33" s="26" t="s">
+      <c r="H33" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="I33" s="55">
+      <c r="I33" s="37">
         <v>100</v>
       </c>
-      <c r="J33" s="85">
+      <c r="J33" s="72">
         <v>2</v>
       </c>
     </row>
@@ -2776,91 +2815,91 @@
       <c r="A34" s="6">
         <v>32</v>
       </c>
-      <c r="B34" s="75" t="s">
-        <v>89</v>
-      </c>
-      <c r="C34" s="33" t="s">
-        <v>73</v>
-      </c>
-      <c r="D34" s="52" t="s">
-        <v>74</v>
-      </c>
-      <c r="E34" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="F34" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="G34" s="66" t="s">
-        <v>29</v>
-      </c>
-      <c r="H34" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="I34" s="13">
-        <v>42</v>
-      </c>
-      <c r="J34" s="86">
+      <c r="B34" s="79"/>
+      <c r="C34" s="34" t="s">
+        <v>240</v>
+      </c>
+      <c r="D34" s="54" t="s">
+        <v>241</v>
+      </c>
+      <c r="E34" s="26" t="s">
+        <v>17</v>
+      </c>
+      <c r="F34" s="26" t="s">
+        <v>242</v>
+      </c>
+      <c r="G34" s="24" t="s">
+        <v>243</v>
+      </c>
+      <c r="H34" s="26" t="s">
+        <v>244</v>
+      </c>
+      <c r="I34" s="55">
+        <v>100</v>
+      </c>
+      <c r="J34" s="73">
         <v>2</v>
       </c>
     </row>
-    <row r="35" spans="1:10" ht="26.25" thickBot="1">
+    <row r="35" spans="1:10" ht="15.75" thickBot="1">
       <c r="A35" s="6">
         <v>33</v>
       </c>
-      <c r="B35" s="76"/>
-      <c r="C35" s="35" t="s">
-        <v>77</v>
-      </c>
-      <c r="D35" s="46" t="s">
-        <v>23</v>
-      </c>
-      <c r="E35" s="17" t="s">
-        <v>78</v>
-      </c>
-      <c r="F35" s="17" t="s">
-        <v>79</v>
-      </c>
-      <c r="G35" s="16" t="s">
-        <v>108</v>
-      </c>
-      <c r="H35" s="17" t="s">
+      <c r="B35" s="77" t="s">
+        <v>89</v>
+      </c>
+      <c r="C35" s="33" t="s">
+        <v>73</v>
+      </c>
+      <c r="D35" s="52" t="s">
+        <v>74</v>
+      </c>
+      <c r="E35" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="F35" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="G35" s="64" t="s">
+        <v>29</v>
+      </c>
+      <c r="H35" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="I35" s="16">
-        <v>21</v>
-      </c>
-      <c r="J35" s="84">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10" ht="15.75" thickBot="1">
+      <c r="I35" s="13">
+        <v>42</v>
+      </c>
+      <c r="J35" s="71">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" ht="26.25" thickBot="1">
       <c r="A36" s="6">
         <v>34</v>
       </c>
-      <c r="B36" s="76"/>
+      <c r="B36" s="78"/>
       <c r="C36" s="35" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D36" s="46" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E36" s="17" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="F36" s="17" t="s">
-        <v>82</v>
-      </c>
-      <c r="G36" s="18" t="s">
-        <v>15</v>
+        <v>79</v>
+      </c>
+      <c r="G36" s="16" t="s">
+        <v>108</v>
       </c>
       <c r="H36" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="I36" s="18">
+      <c r="I36" s="16">
         <v>21</v>
       </c>
-      <c r="J36" s="84">
+      <c r="J36" s="72">
         <v>1</v>
       </c>
     </row>
@@ -2868,18 +2907,18 @@
       <c r="A37" s="6">
         <v>35</v>
       </c>
-      <c r="B37" s="76"/>
+      <c r="B37" s="78"/>
       <c r="C37" s="35" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D37" s="46" t="s">
-        <v>84</v>
+        <v>22</v>
       </c>
       <c r="E37" s="17" t="s">
-        <v>109</v>
+        <v>81</v>
       </c>
       <c r="F37" s="17" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="G37" s="18" t="s">
         <v>15</v>
@@ -2888,61 +2927,61 @@
         <v>15</v>
       </c>
       <c r="I37" s="18">
-        <v>41</v>
-      </c>
-      <c r="J37" s="84">
-        <v>2</v>
+        <v>21</v>
+      </c>
+      <c r="J37" s="72">
+        <v>1</v>
       </c>
     </row>
     <row r="38" spans="1:10" ht="15.75" thickBot="1">
       <c r="A38" s="6">
         <v>36</v>
       </c>
-      <c r="B38" s="76"/>
+      <c r="B38" s="78"/>
       <c r="C38" s="35" t="s">
-        <v>138</v>
+        <v>83</v>
       </c>
       <c r="D38" s="46" t="s">
-        <v>139</v>
+        <v>84</v>
       </c>
       <c r="E38" s="17" t="s">
-        <v>168</v>
+        <v>109</v>
       </c>
       <c r="F38" s="17" t="s">
-        <v>140</v>
+        <v>85</v>
       </c>
       <c r="G38" s="18" t="s">
-        <v>169</v>
+        <v>15</v>
       </c>
       <c r="H38" s="17" t="s">
         <v>15</v>
       </c>
       <c r="I38" s="18">
-        <v>21</v>
-      </c>
-      <c r="J38" s="84">
-        <v>1</v>
+        <v>41</v>
+      </c>
+      <c r="J38" s="72">
+        <v>2</v>
       </c>
     </row>
     <row r="39" spans="1:10" ht="15.75" thickBot="1">
       <c r="A39" s="6">
         <v>37</v>
       </c>
-      <c r="B39" s="76"/>
+      <c r="B39" s="78"/>
       <c r="C39" s="35" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="D39" s="46" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="E39" s="17" t="s">
-        <v>143</v>
+        <v>168</v>
       </c>
       <c r="F39" s="17" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="G39" s="18" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H39" s="17" t="s">
         <v>15</v>
@@ -2950,7 +2989,7 @@
       <c r="I39" s="18">
         <v>21</v>
       </c>
-      <c r="J39" s="84">
+      <c r="J39" s="72">
         <v>1</v>
       </c>
     </row>
@@ -2958,29 +2997,29 @@
       <c r="A40" s="6">
         <v>38</v>
       </c>
-      <c r="B40" s="76"/>
+      <c r="B40" s="78"/>
       <c r="C40" s="35" t="s">
-        <v>220</v>
+        <v>141</v>
       </c>
       <c r="D40" s="46" t="s">
-        <v>221</v>
+        <v>142</v>
       </c>
       <c r="E40" s="17" t="s">
-        <v>21</v>
+        <v>143</v>
       </c>
       <c r="F40" s="17" t="s">
-        <v>222</v>
+        <v>144</v>
       </c>
       <c r="G40" s="18" t="s">
-        <v>30</v>
+        <v>170</v>
       </c>
       <c r="H40" s="17" t="s">
         <v>15</v>
       </c>
       <c r="I40" s="18">
-        <v>22</v>
-      </c>
-      <c r="J40" s="84">
+        <v>21</v>
+      </c>
+      <c r="J40" s="72">
         <v>1</v>
       </c>
     </row>
@@ -2988,151 +3027,151 @@
       <c r="A41" s="6">
         <v>39</v>
       </c>
-      <c r="B41" s="76"/>
-      <c r="C41" s="38" t="s">
-        <v>230</v>
-      </c>
-      <c r="D41" s="68" t="s">
-        <v>228</v>
-      </c>
-      <c r="E41" s="32" t="s">
-        <v>231</v>
-      </c>
-      <c r="F41" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="G41" s="20" t="s">
-        <v>29</v>
+      <c r="B41" s="78"/>
+      <c r="C41" s="35" t="s">
+        <v>220</v>
+      </c>
+      <c r="D41" s="46" t="s">
+        <v>221</v>
+      </c>
+      <c r="E41" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="F41" s="17" t="s">
+        <v>222</v>
+      </c>
+      <c r="G41" s="18" t="s">
+        <v>30</v>
       </c>
       <c r="H41" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="I41" s="20">
-        <v>30</v>
-      </c>
-      <c r="J41" s="84">
+      <c r="I41" s="18">
+        <v>22</v>
+      </c>
+      <c r="J41" s="72">
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:10" ht="26.25" thickBot="1">
+    <row r="42" spans="1:10" ht="15.75" thickBot="1">
       <c r="A42" s="6">
         <v>40</v>
       </c>
-      <c r="B42" s="77"/>
-      <c r="C42" s="34" t="s">
-        <v>86</v>
-      </c>
-      <c r="D42" s="54" t="s">
-        <v>87</v>
-      </c>
-      <c r="E42" s="26" t="s">
-        <v>110</v>
-      </c>
-      <c r="F42" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="G42" s="26" t="s">
-        <v>111</v>
-      </c>
-      <c r="H42" s="26" t="s">
+      <c r="B42" s="78"/>
+      <c r="C42" s="38" t="s">
+        <v>230</v>
+      </c>
+      <c r="D42" s="66" t="s">
+        <v>228</v>
+      </c>
+      <c r="E42" s="32" t="s">
+        <v>231</v>
+      </c>
+      <c r="F42" s="83" t="s">
+        <v>232</v>
+      </c>
+      <c r="G42" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="H42" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="I42" s="24">
+      <c r="I42" s="20">
         <v>30</v>
       </c>
-      <c r="J42" s="85">
+      <c r="J42" s="72">
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:10" ht="15.75" thickBot="1">
+    <row r="43" spans="1:10" ht="26.25" thickBot="1">
       <c r="A43" s="6">
         <v>41</v>
       </c>
-      <c r="B43" s="75" t="s">
-        <v>93</v>
-      </c>
-      <c r="C43" s="33" t="s">
-        <v>90</v>
-      </c>
-      <c r="D43" s="52" t="s">
-        <v>31</v>
-      </c>
-      <c r="E43" s="71" t="s">
-        <v>21</v>
-      </c>
-      <c r="F43" s="58" t="s">
-        <v>91</v>
-      </c>
-      <c r="G43" s="14" t="s">
-        <v>112</v>
-      </c>
-      <c r="H43" s="13" t="s">
+      <c r="B43" s="79"/>
+      <c r="C43" s="34" t="s">
+        <v>86</v>
+      </c>
+      <c r="D43" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="E43" s="26" t="s">
+        <v>110</v>
+      </c>
+      <c r="F43" s="26" t="s">
+        <v>88</v>
+      </c>
+      <c r="G43" s="26" t="s">
+        <v>111</v>
+      </c>
+      <c r="H43" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="I43" s="27">
-        <v>50</v>
-      </c>
-      <c r="J43" s="86">
+      <c r="I43" s="24">
+        <v>30</v>
+      </c>
+      <c r="J43" s="73">
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:10" ht="26.25" thickBot="1">
+    <row r="44" spans="1:10" ht="15.75" thickBot="1">
       <c r="A44" s="6">
         <v>42</v>
       </c>
-      <c r="B44" s="76"/>
-      <c r="C44" s="35" t="s">
-        <v>235</v>
-      </c>
-      <c r="D44" s="46" t="s">
-        <v>32</v>
-      </c>
-      <c r="E44" s="17" t="s">
+      <c r="B44" s="77" t="s">
+        <v>93</v>
+      </c>
+      <c r="C44" s="33" t="s">
+        <v>90</v>
+      </c>
+      <c r="D44" s="52" t="s">
+        <v>31</v>
+      </c>
+      <c r="E44" s="68" t="s">
         <v>21</v>
       </c>
-      <c r="F44" s="17" t="s">
-        <v>236</v>
-      </c>
-      <c r="G44" s="17" t="s">
-        <v>237</v>
-      </c>
-      <c r="H44" s="17" t="s">
+      <c r="F44" s="56" t="s">
+        <v>91</v>
+      </c>
+      <c r="G44" s="14" t="s">
+        <v>112</v>
+      </c>
+      <c r="H44" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="I44" s="17">
-        <v>30</v>
-      </c>
-      <c r="J44" s="84">
+      <c r="I44" s="27">
+        <v>50</v>
+      </c>
+      <c r="J44" s="74">
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:10" ht="15.75" thickBot="1">
+    <row r="45" spans="1:10" ht="26.25" thickBot="1">
       <c r="A45" s="6">
         <v>43</v>
       </c>
-      <c r="B45" s="76"/>
+      <c r="B45" s="78"/>
       <c r="C45" s="35" t="s">
-        <v>92</v>
+        <v>235</v>
       </c>
       <c r="D45" s="46" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="E45" s="17" t="s">
         <v>21</v>
       </c>
       <c r="F45" s="17" t="s">
-        <v>115</v>
+        <v>236</v>
       </c>
       <c r="G45" s="17" t="s">
-        <v>113</v>
+        <v>237</v>
       </c>
       <c r="H45" s="17" t="s">
         <v>15</v>
       </c>
       <c r="I45" s="17">
-        <v>50</v>
-      </c>
-      <c r="J45" s="84">
+        <v>30</v>
+      </c>
+      <c r="J45" s="72">
         <v>1</v>
       </c>
     </row>
@@ -3140,29 +3179,29 @@
       <c r="A46" s="6">
         <v>44</v>
       </c>
-      <c r="B46" s="76"/>
+      <c r="B46" s="78"/>
       <c r="C46" s="35" t="s">
-        <v>223</v>
+        <v>92</v>
       </c>
       <c r="D46" s="46" t="s">
-        <v>224</v>
+        <v>26</v>
       </c>
       <c r="E46" s="17" t="s">
         <v>21</v>
       </c>
       <c r="F46" s="17" t="s">
-        <v>225</v>
+        <v>115</v>
       </c>
       <c r="G46" s="17" t="s">
-        <v>226</v>
+        <v>113</v>
       </c>
       <c r="H46" s="17" t="s">
         <v>15</v>
       </c>
       <c r="I46" s="17">
-        <v>25</v>
-      </c>
-      <c r="J46" s="84">
+        <v>50</v>
+      </c>
+      <c r="J46" s="72">
         <v>1</v>
       </c>
     </row>
@@ -3170,127 +3209,151 @@
       <c r="A47" s="6">
         <v>45</v>
       </c>
-      <c r="B47" s="76"/>
-      <c r="C47" s="38" t="s">
-        <v>233</v>
-      </c>
-      <c r="D47" s="69" t="s">
-        <v>229</v>
+      <c r="B47" s="78"/>
+      <c r="C47" s="35" t="s">
+        <v>223</v>
+      </c>
+      <c r="D47" s="46" t="s">
+        <v>224</v>
       </c>
       <c r="E47" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="F47" s="70">
-        <v>61300611121</v>
-      </c>
-      <c r="G47" s="32" t="s">
-        <v>234</v>
+      <c r="F47" s="17" t="s">
+        <v>225</v>
+      </c>
+      <c r="G47" s="17" t="s">
+        <v>226</v>
       </c>
       <c r="H47" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="I47" s="32">
-        <v>40</v>
-      </c>
-      <c r="J47" s="84">
+      <c r="I47" s="17">
+        <v>25</v>
+      </c>
+      <c r="J47" s="72">
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:10" ht="102.75" thickBot="1">
+    <row r="48" spans="1:10" ht="15.75" thickBot="1">
       <c r="A48" s="6">
         <v>46</v>
       </c>
-      <c r="B48" s="77"/>
-      <c r="C48" s="40" t="s">
-        <v>27</v>
-      </c>
-      <c r="D48" s="41" t="s">
-        <v>198</v>
-      </c>
-      <c r="E48" s="42" t="s">
-        <v>28</v>
-      </c>
-      <c r="F48" s="42" t="s">
-        <v>28</v>
-      </c>
-      <c r="G48" s="43"/>
-      <c r="H48" s="44" t="s">
-        <v>30</v>
-      </c>
-      <c r="I48" s="44" t="s">
+      <c r="B48" s="78"/>
+      <c r="C48" s="38" t="s">
+        <v>233</v>
+      </c>
+      <c r="D48" s="67" t="s">
+        <v>229</v>
+      </c>
+      <c r="E48" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="F48" s="87">
+        <v>61300611121</v>
+      </c>
+      <c r="G48" s="32" t="s">
+        <v>234</v>
+      </c>
+      <c r="H48" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="J48" s="85">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="49" spans="1:10" ht="26.25" thickBot="1">
+      <c r="I48" s="32">
+        <v>40</v>
+      </c>
+      <c r="J48" s="72">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" ht="102.75" thickBot="1">
       <c r="A49" s="6">
         <v>47</v>
       </c>
-      <c r="B49" s="73" t="s">
+      <c r="B49" s="79"/>
+      <c r="C49" s="40" t="s">
+        <v>27</v>
+      </c>
+      <c r="D49" s="41" t="s">
+        <v>198</v>
+      </c>
+      <c r="E49" s="42" t="s">
+        <v>28</v>
+      </c>
+      <c r="F49" s="42" t="s">
+        <v>28</v>
+      </c>
+      <c r="G49" s="43"/>
+      <c r="H49" s="44" t="s">
+        <v>30</v>
+      </c>
+      <c r="I49" s="44" t="s">
+        <v>15</v>
+      </c>
+      <c r="J49" s="73">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" ht="26.25" thickBot="1">
+      <c r="A50" s="6">
+        <v>48</v>
+      </c>
+      <c r="B50" s="75" t="s">
         <v>117</v>
       </c>
-      <c r="C49" s="62" t="s">
+      <c r="C50" s="60" t="s">
         <v>201</v>
       </c>
-      <c r="D49" s="63" t="s">
+      <c r="D50" s="61" t="s">
         <v>30</v>
       </c>
-      <c r="E49" s="63" t="s">
+      <c r="E50" s="61" t="s">
         <v>30</v>
       </c>
-      <c r="F49" s="63" t="s">
+      <c r="F50" s="61" t="s">
         <v>200</v>
       </c>
-      <c r="G49" s="63" t="s">
+      <c r="G50" s="61" t="s">
         <v>114</v>
       </c>
-      <c r="H49" s="63" t="s">
+      <c r="H50" s="61" t="s">
         <v>114</v>
       </c>
-      <c r="I49" s="63" t="s">
+      <c r="I50" s="61" t="s">
         <v>114</v>
       </c>
-      <c r="J49" s="86">
+      <c r="J50" s="74">
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:10" ht="15.75" thickBot="1">
-      <c r="A50" s="72">
-        <v>48</v>
-      </c>
-      <c r="B50" s="74"/>
-      <c r="C50" s="64" t="s">
+    <row r="51" spans="1:10" ht="15.75" thickBot="1">
+      <c r="A51" s="88">
+        <v>49</v>
+      </c>
+      <c r="B51" s="76"/>
+      <c r="C51" s="62" t="s">
         <v>118</v>
       </c>
-      <c r="D50" s="65" t="s">
+      <c r="D51" s="63" t="s">
         <v>30</v>
       </c>
-      <c r="E50" s="65" t="s">
+      <c r="E51" s="63" t="s">
         <v>30</v>
       </c>
-      <c r="F50" s="65" t="s">
+      <c r="F51" s="63" t="s">
         <v>118</v>
       </c>
-      <c r="G50" s="65" t="s">
+      <c r="G51" s="63" t="s">
         <v>30</v>
       </c>
-      <c r="H50" s="65" t="s">
+      <c r="H51" s="63" t="s">
         <v>30</v>
       </c>
-      <c r="I50" s="65" t="s">
+      <c r="I51" s="63" t="s">
         <v>15</v>
       </c>
-      <c r="J50" s="85">
+      <c r="J51" s="73">
         <v>1</v>
       </c>
-    </row>
-    <row r="51" spans="1:10">
-      <c r="A51" s="1"/>
-      <c r="C51" s="2"/>
-      <c r="D51" s="2"/>
-      <c r="I51" s="7"/>
     </row>
     <row r="52" spans="1:10">
       <c r="A52" s="1"/>
@@ -3302,6 +3365,7 @@
       <c r="A53" s="1"/>
       <c r="C53" s="2"/>
       <c r="D53" s="2"/>
+      <c r="I53" s="7"/>
     </row>
     <row r="54" spans="1:10">
       <c r="A54" s="1"/>
@@ -3325,11 +3389,13 @@
     </row>
     <row r="58" spans="1:10">
       <c r="A58" s="1"/>
-    </row>
-    <row r="59" spans="1:10" ht="15.75" customHeight="1">
+      <c r="C58" s="2"/>
+      <c r="D58" s="2"/>
+    </row>
+    <row r="59" spans="1:10">
       <c r="A59" s="1"/>
     </row>
-    <row r="60" spans="1:10">
+    <row r="60" spans="1:10" ht="15.75" customHeight="1">
       <c r="A60" s="1"/>
     </row>
     <row r="61" spans="1:10">
@@ -3344,26 +3410,29 @@
     <row r="64" spans="1:10">
       <c r="A64" s="1"/>
     </row>
-    <row r="65" spans="7:7">
-      <c r="G65" s="8"/>
-    </row>
-    <row r="66" spans="7:7">
+    <row r="65" spans="1:7">
+      <c r="A65" s="1"/>
+    </row>
+    <row r="66" spans="1:7">
       <c r="G66" s="8"/>
+    </row>
+    <row r="67" spans="1:7">
+      <c r="G67" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="B29:B34"/>
+    <mergeCell ref="B50:B51"/>
     <mergeCell ref="B3:B17"/>
     <mergeCell ref="B20:B23"/>
-    <mergeCell ref="B29:B33"/>
-    <mergeCell ref="B34:B42"/>
-    <mergeCell ref="B43:B48"/>
+    <mergeCell ref="B35:B43"/>
+    <mergeCell ref="B44:B49"/>
     <mergeCell ref="B26:B28"/>
     <mergeCell ref="B18:B19"/>
-    <mergeCell ref="A1:J1"/>
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
-  <conditionalFormatting sqref="I48">
+  <conditionalFormatting sqref="I49">
     <cfRule type="dataBar" priority="59">
       <dataBar>
         <cfvo type="min"/>
@@ -3393,7 +3462,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I48</xm:sqref>
+          <xm:sqref>I49</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
